--- a/open_trial_kit_parts.xlsx
+++ b/open_trial_kit_parts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\atmobi\ドキュメント\ハードウエア開発\オープンハードウエア台車\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Qiita\open_trial_kit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD5CCCF-C2D8-488D-BD86-13E9E302F17F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57350C7B-5CFB-4632-951C-70C96429BE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
+    <workbookView xWindow="-9870" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="オープンハードウエア部材リスト" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="211">
   <si>
     <t>モーター</t>
     <phoneticPr fontId="3"/>
@@ -320,16 +320,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>12日納期</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>センターボルト</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -617,26 +607,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>8日納期</t>
-    <rPh sb="1" eb="2">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>3日納期</t>
-    <rPh sb="1" eb="2">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MVSHM-AW05001-3WF-EFSA2</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -819,10 +789,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>MVTUP-APW-3Y5-EEN3W</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>緩衝キャスター SAJ-TS6-SJ-50R</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -934,16 +900,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>21日納期だと @6334</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>MVBLK-ABN-3Y6-E6DKS</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -970,55 +926,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>６日納期</t>
-    <rPh sb="1" eb="2">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>20日納期</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>5日納期</t>
-    <rPh sb="1" eb="2">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>10日納期</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>接続ケーブル(30cm)</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>PCベース</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MVSHM-3N03000-3Y6-7UL4T</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1162,7 +1074,7 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>その他調達部材(※パナソニックアドバンストテクノロジーからの提供価格)</t>
+    <t>その他調達部材(センサー例)</t>
     <rPh sb="2" eb="3">
       <t>ホカ</t>
     </rPh>
@@ -1172,6 +1084,27 @@
     <rPh sb="5" eb="7">
       <t>ブザイ</t>
     </rPh>
+    <rPh sb="12" eb="13">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MVTUP-APW-456-7J5B4</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>価格は 2025/4 現在のものです</t>
+    <rPh sb="0" eb="2">
+      <t>カカク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>MVSHM-3N03000-456-YRTZX</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1179,7 +1112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1272,6 +1205,15 @@
       <color theme="0"/>
       <name val="游ゴシック"/>
       <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -1442,7 +1384,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1545,6 +1487,27 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1587,25 +1550,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1940,82 +1885,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B1" s="37" t="s">
+      <c r="H1" s="55" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B2" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="37"/>
-      <c r="D1" s="7" t="s">
+      <c r="C2" s="44"/>
+      <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="G2" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="21" t="s">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B3" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="24">
-        <f>SUM(I3:I7)</f>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="24">
+        <f>SUM(I4:I8)</f>
         <v>133740</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="38"/>
-      <c r="C3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>2</v>
-      </c>
-      <c r="G3" s="5">
-        <v>2</v>
-      </c>
-      <c r="H3" s="6">
-        <v>27620</v>
-      </c>
-      <c r="I3" s="20">
-        <f>G3*H3</f>
-        <v>55240</v>
-      </c>
-      <c r="J3" t="s">
-        <v>184</v>
-      </c>
-    </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="39"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4" s="5">
         <v>2</v>
@@ -2024,706 +1946,703 @@
         <v>2</v>
       </c>
       <c r="H4" s="6">
-        <v>32130</v>
+        <v>27620</v>
       </c>
       <c r="I4" s="20">
-        <f t="shared" ref="I4:I7" si="0">G4*H4</f>
-        <v>64260</v>
-      </c>
-      <c r="J4" t="s">
-        <v>185</v>
+        <f>G4*H4</f>
+        <v>55240</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="39"/>
+      <c r="B5" s="46"/>
       <c r="C5" s="5" t="s">
-        <v>187</v>
+        <v>3</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>2</v>
+      </c>
+      <c r="G5" s="5">
+        <v>2</v>
+      </c>
+      <c r="H5" s="6">
+        <v>32130</v>
+      </c>
+      <c r="I5" s="20">
+        <f t="shared" ref="I5:I8" si="0">G5*H5</f>
+        <v>64260</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="46"/>
+      <c r="C6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="6">
+      <c r="F6" s="5">
+        <v>2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>2</v>
+      </c>
+      <c r="H6" s="6">
         <v>2720</v>
       </c>
-      <c r="I5" s="20">
+      <c r="I6" s="20">
         <f t="shared" si="0"/>
         <v>5440</v>
       </c>
-      <c r="J5" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="39"/>
-      <c r="C6" s="5" t="s">
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="46"/>
+      <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="5">
-        <v>2</v>
-      </c>
-      <c r="G6" s="5">
-        <v>2</v>
-      </c>
-      <c r="H6" s="6">
+      <c r="F7" s="5">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>2</v>
+      </c>
+      <c r="H7" s="6">
         <v>2800</v>
       </c>
-      <c r="I6" s="20">
+      <c r="I7" s="20">
         <f t="shared" si="0"/>
         <v>5600</v>
       </c>
-      <c r="J6" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="40"/>
-      <c r="C7" s="5" t="s">
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="47"/>
+      <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="5">
-        <v>2</v>
-      </c>
-      <c r="G7" s="5">
-        <v>2</v>
-      </c>
-      <c r="H7" s="6">
+      <c r="F8" s="5">
+        <v>2</v>
+      </c>
+      <c r="G8" s="5">
+        <v>2</v>
+      </c>
+      <c r="H8" s="6">
         <v>1600</v>
       </c>
-      <c r="I7" s="20">
+      <c r="I8" s="20">
         <f t="shared" si="0"/>
         <v>3200</v>
       </c>
-      <c r="J7" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="19" t="s">
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B9" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="25">
-        <f>SUM(I9:I20)</f>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="25">
+        <f>SUM(I10:I21)</f>
         <v>38280</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="41"/>
-      <c r="C9" s="2" t="s">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B10" s="48"/>
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="2">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2</v>
-      </c>
-      <c r="H9" s="26">
+      <c r="F10" s="2">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>2</v>
+      </c>
+      <c r="H10" s="26">
         <v>2490</v>
       </c>
-      <c r="I9" s="3">
-        <f>G9*H9</f>
+      <c r="I10" s="3">
+        <f>G10*H10</f>
         <v>4980</v>
       </c>
-      <c r="J9" s="32" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B10" s="41"/>
-      <c r="C10" s="2" t="s">
+      <c r="J10" s="32" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B11" s="48"/>
+      <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F10" s="2">
-        <v>1</v>
-      </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="E11" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
         <v>14900</v>
       </c>
-      <c r="I10" s="3">
-        <f t="shared" ref="I10:I20" si="1">G10*H10</f>
+      <c r="I11" s="3">
+        <f t="shared" ref="I11:I21" si="1">G11*H11</f>
         <v>14900</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B11" s="41"/>
-      <c r="C11" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="J11" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B12" s="48"/>
+      <c r="C12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
         <v>2172</v>
       </c>
-      <c r="I11" s="3">
+      <c r="I12" s="3">
         <f t="shared" si="1"/>
         <v>2172</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B12" s="41"/>
-      <c r="C12" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="J12" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B13" s="48"/>
+      <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F12" s="2">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3">
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
         <v>1600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I13" s="3">
         <f t="shared" si="1"/>
         <v>1600</v>
       </c>
-      <c r="J12" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="K12" s="9" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B13" s="41"/>
-      <c r="C13" s="2" t="s">
+      <c r="J13" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B14" s="48"/>
+      <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F13" s="2">
-        <v>1</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3">
+      <c r="F14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
         <v>6312</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I14" s="3">
         <f t="shared" si="1"/>
         <v>6312</v>
       </c>
-      <c r="J13" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="41"/>
-      <c r="C14" s="2" t="s">
+      <c r="J14" s="15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B15" s="48"/>
+      <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2">
-        <v>1</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
         <v>695</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I15" s="3">
         <f t="shared" si="1"/>
         <v>695</v>
       </c>
-      <c r="J14" s="18" t="s">
+      <c r="J15" s="18" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="41"/>
-      <c r="C15" s="2" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B16" s="48"/>
+      <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F15" s="2">
-        <v>1</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
+      <c r="F16" s="2">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
         <v>1540</v>
       </c>
-      <c r="I15" s="3">
+      <c r="I16" s="3">
         <f t="shared" si="1"/>
         <v>1540</v>
       </c>
-      <c r="J15" s="18" t="s">
+      <c r="J16" s="18" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B16" s="41"/>
-      <c r="C16" s="2" t="s">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B17" s="48"/>
+      <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="2">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="F17" s="2">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
         <v>2337</v>
       </c>
-      <c r="I16" s="3">
+      <c r="I17" s="3">
         <f t="shared" si="1"/>
         <v>2337</v>
       </c>
-      <c r="J16" s="18" t="s">
+      <c r="J17" s="18" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="41"/>
-      <c r="C17" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E17" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="F17" s="2">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B18" s="48"/>
+      <c r="C18" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F18" s="2">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
         <v>1599</v>
       </c>
-      <c r="I17" s="3">
+      <c r="I18" s="3">
         <f t="shared" si="1"/>
         <v>1599</v>
       </c>
-      <c r="J17" s="18" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="41"/>
-      <c r="C18" s="2" t="s">
+      <c r="J18" s="18" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B19" s="48"/>
+      <c r="C19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="2">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2">
-        <v>1</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="F19" s="2">
+        <v>1</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
         <v>1690</v>
       </c>
-      <c r="I18" s="3">
+      <c r="I19" s="3">
         <f t="shared" si="1"/>
         <v>1690</v>
       </c>
-      <c r="J18" s="18" t="s">
+      <c r="J19" s="18" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="41"/>
-      <c r="C19" s="2" t="s">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B20" s="48"/>
+      <c r="C20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
         <v>229</v>
       </c>
-      <c r="I19" s="3">
+      <c r="I20" s="3">
         <f t="shared" si="1"/>
         <v>229</v>
       </c>
-      <c r="J19" s="18" t="s">
+      <c r="J20" s="18" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="41"/>
-      <c r="C20" s="2" t="s">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B21" s="48"/>
+      <c r="C21" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F20" s="2">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="E21" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
         <v>226</v>
       </c>
-      <c r="I20" s="3">
+      <c r="I21" s="3">
         <f t="shared" si="1"/>
         <v>226</v>
       </c>
-      <c r="J20" s="18" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="24">
-        <f>SUM(I23:I26)</f>
-        <v>1262</v>
+      <c r="J21" s="18" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="42"/>
-      <c r="C22" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="F22" s="5">
-        <v>1</v>
-      </c>
-      <c r="G22" s="5">
-        <v>1</v>
-      </c>
-      <c r="H22" s="5">
+      <c r="B22" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="24">
+        <f>SUM(I23:I27)</f>
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B23" s="49"/>
+      <c r="C23" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5">
+        <v>1</v>
+      </c>
+      <c r="H23" s="5">
         <v>2925</v>
       </c>
-      <c r="I22" s="6">
-        <f>G22*H22</f>
+      <c r="I23" s="6">
+        <f>G23*H23</f>
         <v>2925</v>
       </c>
-      <c r="J22" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="43"/>
-      <c r="C23" s="5" t="s">
+      <c r="J23" s="9" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B24" s="50"/>
+      <c r="C24" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F24" s="5">
+        <v>5</v>
+      </c>
+      <c r="G24" s="5">
+        <v>5</v>
+      </c>
+      <c r="H24" s="6">
+        <v>96</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" ref="I24:I27" si="2">G24*H24</f>
+        <v>480</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B25" s="50"/>
+      <c r="C25" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="5">
-        <v>5</v>
-      </c>
-      <c r="G23" s="5">
-        <v>5</v>
-      </c>
-      <c r="H23" s="6">
-        <v>96</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" ref="I23:I26" si="2">G23*H23</f>
-        <v>480</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="43"/>
-      <c r="C24" s="5" t="s">
+      <c r="D25" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="D24" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="F24" s="5">
-        <v>2</v>
-      </c>
-      <c r="G24" s="5">
-        <v>2</v>
-      </c>
-      <c r="H24" s="6">
+      <c r="F25" s="5">
+        <v>2</v>
+      </c>
+      <c r="G25" s="5">
+        <v>2</v>
+      </c>
+      <c r="H25" s="6">
         <v>54</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I25" s="6">
         <f t="shared" si="2"/>
         <v>108</v>
       </c>
-      <c r="J24" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="43"/>
-      <c r="C25" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" s="28" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" s="5">
+      <c r="J25" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B26" s="50"/>
+      <c r="C26" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="5">
         <v>4</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G26" s="5">
         <v>4</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H26" s="6">
         <v>99</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I26" s="6">
         <f t="shared" si="2"/>
         <v>396</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J26" s="9" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B27" s="51"/>
+      <c r="C27" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="28" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="44"/>
-      <c r="C26" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="5">
-        <v>2</v>
-      </c>
-      <c r="G26" s="5">
-        <v>2</v>
-      </c>
-      <c r="H26" s="6">
+      <c r="F27" s="5">
+        <v>2</v>
+      </c>
+      <c r="G27" s="5">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6">
         <v>139</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I27" s="6">
         <f t="shared" si="2"/>
         <v>278</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="19" t="s">
+      <c r="J27" s="9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B28" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="25">
-        <f>SUM(I28)</f>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="25">
+        <f>SUM(I29)</f>
         <v>29568</v>
       </c>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="23"/>
-      <c r="C28" s="2" t="s">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B29" s="23"/>
+      <c r="C29" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="2">
-        <v>1</v>
-      </c>
-      <c r="G28" s="2">
-        <v>1</v>
-      </c>
-      <c r="H28" s="26">
+      <c r="E29" s="4"/>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>1</v>
+      </c>
+      <c r="H29" s="26">
         <v>29568</v>
       </c>
-      <c r="I28" s="16">
-        <f>G28*H28</f>
+      <c r="I29" s="16">
+        <f>G29*H29</f>
         <v>29568</v>
       </c>
-      <c r="J28" s="17" t="s">
+      <c r="J29" s="17" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="21" t="s">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B30" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="22"/>
-      <c r="H29" s="22"/>
-      <c r="I29" s="24">
-        <f>SUM(I30:I35)</f>
-        <v>30838</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="38"/>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="22"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="24">
+        <f>SUM(I31:I35)</f>
+        <v>47632</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B31" s="45"/>
+      <c r="C31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="F30" s="5">
-        <v>2</v>
-      </c>
-      <c r="G30" s="5">
-        <v>2</v>
-      </c>
-      <c r="H30" s="6">
-        <v>7037</v>
-      </c>
-      <c r="I30" s="6">
-        <f>G30*H30</f>
-        <v>14074</v>
-      </c>
-      <c r="J30" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="39"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" t="s">
-        <v>177</v>
+      <c r="E31" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F31" s="5">
+        <v>2</v>
+      </c>
+      <c r="G31" s="5">
+        <v>2</v>
+      </c>
+      <c r="H31" s="6">
+        <v>15434</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" ref="I31:I35" si="3">G31*H31</f>
+        <v>30868</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="39"/>
+      <c r="B32" s="46"/>
       <c r="C32" s="5" t="s">
         <v>55</v>
       </c>
@@ -2743,23 +2662,23 @@
         <v>510</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" ref="I32:I35" si="3">G32*H32</f>
+        <f t="shared" si="3"/>
         <v>1020</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="39"/>
+      <c r="B33" s="46"/>
       <c r="C33" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F33" s="5">
         <v>2</v>
@@ -2775,19 +2694,19 @@
         <v>11020</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="39"/>
+      <c r="B34" s="46"/>
       <c r="C34" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F34" s="5">
         <v>2</v>
@@ -2803,11 +2722,11 @@
         <v>72</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="40"/>
+      <c r="B35" s="47"/>
       <c r="C35" s="5" t="s">
         <v>21</v>
       </c>
@@ -2815,7 +2734,7 @@
         <v>38</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F35" s="5">
         <v>2</v>
@@ -2831,7 +2750,7 @@
         <v>4652</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
@@ -2846,19 +2765,19 @@
       <c r="H36" s="10"/>
       <c r="I36" s="25">
         <f>SUM(I37:I68)</f>
-        <v>70815</v>
+        <v>70777</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="45"/>
+      <c r="B37" s="52"/>
       <c r="C37" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D37" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F37" s="2">
         <v>1</v>
@@ -2873,20 +2792,17 @@
         <f>G37*H37</f>
         <v>10832</v>
       </c>
-      <c r="J37" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="46"/>
+      <c r="B38" s="53"/>
       <c r="C38" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F38" s="2">
         <v>1</v>
@@ -2901,12 +2817,9 @@
         <f t="shared" ref="I38:I68" si="4">G38*H38</f>
         <v>5842</v>
       </c>
-      <c r="J38" t="s">
-        <v>114</v>
-      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="46"/>
+      <c r="B39" s="53"/>
       <c r="C39" s="2" t="s">
         <v>54</v>
       </c>
@@ -2914,7 +2827,7 @@
         <v>53</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -2929,20 +2842,17 @@
         <f t="shared" si="4"/>
         <v>8629</v>
       </c>
-      <c r="J39" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="46"/>
+      <c r="B40" s="53"/>
       <c r="C40" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -2957,20 +2867,17 @@
         <f t="shared" si="4"/>
         <v>3268</v>
       </c>
-      <c r="J40" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="46"/>
+      <c r="B41" s="53"/>
       <c r="C41" s="2" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
@@ -2979,26 +2886,23 @@
         <v>1</v>
       </c>
       <c r="H41" s="3">
-        <v>2462</v>
+        <v>2424</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="4"/>
-        <v>2462</v>
-      </c>
-      <c r="J41" t="s">
-        <v>183</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="46"/>
+      <c r="B42" s="53"/>
       <c r="C42" s="2" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -3013,20 +2917,17 @@
         <f t="shared" si="4"/>
         <v>2527</v>
       </c>
-      <c r="J42" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="46"/>
+      <c r="B43" s="53"/>
       <c r="C43" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="F43" s="2">
         <v>2</v>
@@ -3041,20 +2942,17 @@
         <f t="shared" si="4"/>
         <v>6816</v>
       </c>
-      <c r="J43" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="46"/>
+      <c r="B44" s="53"/>
       <c r="C44" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>53</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F44" s="2">
         <v>2</v>
@@ -3069,20 +2967,17 @@
         <f t="shared" si="4"/>
         <v>5412</v>
       </c>
-      <c r="J44" t="s">
-        <v>183</v>
-      </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="46"/>
+      <c r="B45" s="53"/>
       <c r="C45" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D45" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F45" s="2">
         <v>2</v>
@@ -3098,19 +2993,19 @@
         <v>2960</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="46"/>
+      <c r="B46" s="53"/>
       <c r="C46" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D46" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F46" s="2">
         <v>3</v>
@@ -3126,19 +3021,19 @@
         <v>5823</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="46"/>
+      <c r="B47" s="53"/>
       <c r="C47" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="F47" s="2">
         <v>1</v>
@@ -3154,19 +3049,19 @@
         <v>736</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="46"/>
+      <c r="B48" s="53"/>
       <c r="C48" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F48" s="2">
         <v>2</v>
@@ -3182,19 +3077,19 @@
         <v>4620</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="46"/>
+      <c r="B49" s="53"/>
       <c r="C49" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -3210,19 +3105,19 @@
         <v>380</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="46"/>
+      <c r="B50" s="53"/>
       <c r="C50" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F50" s="2">
         <v>2</v>
@@ -3238,19 +3133,19 @@
         <v>356</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="46"/>
+      <c r="B51" s="53"/>
       <c r="C51" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D51" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F51" s="2">
         <v>4</v>
@@ -3266,19 +3161,19 @@
         <v>712</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="46"/>
+      <c r="B52" s="53"/>
       <c r="C52" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D52" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F52" s="2">
         <v>15</v>
@@ -3294,19 +3189,19 @@
         <v>1350</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="46"/>
+      <c r="B53" s="53"/>
       <c r="C53" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D53" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F53" s="2">
         <v>10</v>
@@ -3322,19 +3217,19 @@
         <v>1400</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="46"/>
+      <c r="B54" s="53"/>
       <c r="C54" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D54" s="29" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E54" s="30" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F54" s="2">
         <v>1</v>
@@ -3350,19 +3245,19 @@
         <v>792</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="46"/>
+      <c r="B55" s="53"/>
       <c r="C55" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D55" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F55" s="2">
         <v>7</v>
@@ -3378,19 +3273,19 @@
         <v>360</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="46"/>
+      <c r="B56" s="53"/>
       <c r="C56" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F56" s="2">
         <v>2</v>
@@ -3406,19 +3301,19 @@
         <v>68</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="46"/>
+      <c r="B57" s="53"/>
       <c r="C57" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D57" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F57" s="2">
         <v>4</v>
@@ -3434,19 +3329,19 @@
         <v>360</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="46"/>
+      <c r="B58" s="53"/>
       <c r="C58" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D58" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F58" s="2">
         <v>28</v>
@@ -3462,19 +3357,19 @@
         <v>952</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="46"/>
+      <c r="B59" s="53"/>
       <c r="C59" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D59" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F59" s="2">
         <v>8</v>
@@ -3490,19 +3385,19 @@
         <v>360</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="46"/>
+      <c r="B60" s="53"/>
       <c r="C60" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D60" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F60" s="2">
         <v>2</v>
@@ -3518,19 +3413,19 @@
         <v>162</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="46"/>
+      <c r="B61" s="53"/>
       <c r="C61" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D61" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F61" s="2">
         <v>2</v>
@@ -3546,19 +3441,19 @@
         <v>340</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="46"/>
+      <c r="B62" s="53"/>
       <c r="C62" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D62" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
@@ -3574,19 +3469,19 @@
         <v>204</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="46"/>
+      <c r="B63" s="53"/>
       <c r="C63" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D63" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F63" s="2">
         <v>4</v>
@@ -3602,19 +3497,19 @@
         <v>196</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="46"/>
+      <c r="B64" s="53"/>
       <c r="C64" s="2" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D64" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F64" s="2">
         <f>7+20+6</f>
@@ -3631,19 +3526,19 @@
         <v>1320</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B65" s="46"/>
+      <c r="B65" s="53"/>
       <c r="C65" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D65" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F65" s="2">
         <v>4</v>
@@ -3659,19 +3554,19 @@
         <v>208</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B66" s="46"/>
+      <c r="B66" s="53"/>
       <c r="C66" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D66" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F66" s="2">
         <v>2</v>
@@ -3687,19 +3582,19 @@
         <v>482</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B67" s="46"/>
+      <c r="B67" s="53"/>
       <c r="C67" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F67" s="2">
         <v>2</v>
@@ -3715,19 +3610,19 @@
         <v>478</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B68" s="47"/>
+      <c r="B68" s="54"/>
       <c r="C68" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D68" s="10" t="s">
         <v>24</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F68" s="2">
         <v>6</v>
@@ -3743,12 +3638,12 @@
         <v>408</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B69" s="21" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C69" s="22"/>
       <c r="D69" s="22"/>
@@ -3762,15 +3657,15 @@
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B70" s="38"/>
+      <c r="B70" s="45"/>
       <c r="C70" s="5" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F70" s="5">
         <v>1</v>
@@ -3787,15 +3682,15 @@
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B71" s="39"/>
+      <c r="B71" s="46"/>
       <c r="C71" s="5" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D71" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F71" s="5">
         <v>3</v>
@@ -3811,19 +3706,19 @@
         <v>1500</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B72" s="39"/>
+      <c r="B72" s="46"/>
       <c r="C72" s="5" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F72" s="5">
         <v>3</v>
@@ -3835,23 +3730,23 @@
         <v>68</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" ref="I72:I75" si="5">G72*H72</f>
+        <f t="shared" ref="I72:I74" si="5">G72*H72</f>
         <v>204</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B73" s="39"/>
+      <c r="B73" s="46"/>
       <c r="C73" s="5" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D73" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F73" s="5">
         <v>6</v>
@@ -3867,19 +3762,19 @@
         <v>240</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B74" s="39"/>
+      <c r="B74" s="46"/>
       <c r="C74" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F74" s="5">
         <v>6</v>
@@ -3895,19 +3790,19 @@
         <v>204</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B75" s="40"/>
+      <c r="B75" s="47"/>
       <c r="C75" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F75" s="5">
         <v>3</v>
@@ -3923,7 +3818,7 @@
         <v>420</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.4">
@@ -3937,47 +3832,47 @@
       <c r="I76" s="12"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B77" s="34" t="s">
+      <c r="B77" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="C77" s="35"/>
-      <c r="D77" s="35"/>
-      <c r="E77" s="35"/>
-      <c r="F77" s="36"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="43"/>
       <c r="G77" s="31"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14">
-        <f>I2+I8+I21+I27+I29+I36+I69</f>
-        <v>314706</v>
+        <f>I3+I9+I22+I28+I30+I36+I69</f>
+        <v>334387</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A79" s="48" t="s">
-        <v>217</v>
+      <c r="A79" s="34" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B80" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="C80" s="54"/>
-      <c r="D80" s="51"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="51"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="52"/>
-      <c r="I80" s="52"/>
+      <c r="B80" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="C80" s="40"/>
+      <c r="D80" s="35"/>
+      <c r="E80" s="35"/>
+      <c r="F80" s="35"/>
+      <c r="G80" s="35"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B81" s="49"/>
+      <c r="B81" s="37"/>
       <c r="C81" s="2" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F81" s="2">
         <v>1</v>
@@ -3985,24 +3880,19 @@
       <c r="G81" s="2">
         <v>1</v>
       </c>
-      <c r="H81" s="3">
-        <v>130000</v>
-      </c>
-      <c r="I81" s="3">
-        <f>G81*H81</f>
-        <v>130000</v>
-      </c>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B82" s="50"/>
+      <c r="B82" s="38"/>
       <c r="C82" s="2" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F82" s="2">
         <v>1</v>
@@ -4010,15 +3900,10 @@
       <c r="G82" s="2">
         <v>1</v>
       </c>
-      <c r="H82" s="3">
-        <v>10000</v>
-      </c>
-      <c r="I82" s="3">
-        <f>G82*H82</f>
-        <v>10000</v>
-      </c>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
       <c r="J82" s="9" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -4026,22 +3911,22 @@
     <mergeCell ref="B81:B82"/>
     <mergeCell ref="B80:C80"/>
     <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B9:B20"/>
-    <mergeCell ref="B30:B35"/>
-    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B10:B21"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B23:B27"/>
     <mergeCell ref="B37:B68"/>
     <mergeCell ref="B70:B75"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="J28" r:id="rId1" xr:uid="{16F66288-6245-48F6-9127-58AACEC69523}"/>
-    <hyperlink ref="J14" r:id="rId2" xr:uid="{63D6F597-30D0-478D-AD7F-BE9842A28425}"/>
-    <hyperlink ref="J18" r:id="rId3" xr:uid="{A288C923-0EA8-47B0-95FF-F697D2BA3F3D}"/>
-    <hyperlink ref="J16" r:id="rId4" xr:uid="{FDEE0E6F-A921-416C-95B6-8808A9B8EF28}"/>
-    <hyperlink ref="J19" r:id="rId5" xr:uid="{CC25CD88-C4A6-4402-9EAF-CF9F03244A94}"/>
-    <hyperlink ref="J15" r:id="rId6" xr:uid="{8B264363-2167-4322-AC9D-61EEEB1F631E}"/>
+    <hyperlink ref="J29" r:id="rId1" xr:uid="{16F66288-6245-48F6-9127-58AACEC69523}"/>
+    <hyperlink ref="J15" r:id="rId2" xr:uid="{63D6F597-30D0-478D-AD7F-BE9842A28425}"/>
+    <hyperlink ref="J19" r:id="rId3" xr:uid="{A288C923-0EA8-47B0-95FF-F697D2BA3F3D}"/>
+    <hyperlink ref="J17" r:id="rId4" xr:uid="{FDEE0E6F-A921-416C-95B6-8808A9B8EF28}"/>
+    <hyperlink ref="J20" r:id="rId5" xr:uid="{CC25CD88-C4A6-4402-9EAF-CF9F03244A94}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{8B264363-2167-4322-AC9D-61EEEB1F631E}"/>
     <hyperlink ref="J33" r:id="rId7" xr:uid="{A66669A8-27A1-4491-BF8D-462003BC8225}"/>
     <hyperlink ref="J52" r:id="rId8" xr:uid="{D484C0DB-C886-4F67-B728-6E53738B4676}"/>
     <hyperlink ref="J46" r:id="rId9" xr:uid="{D5216D90-A293-4CC2-B82E-7064EFFDA08C}"/>
@@ -4057,37 +3942,37 @@
     <hyperlink ref="J55" r:id="rId19" xr:uid="{D197653E-A28E-4309-8A92-274076756833}"/>
     <hyperlink ref="J51" r:id="rId20" xr:uid="{4A67E8D4-9CDB-42BA-BC51-D3ED5858EB3C}"/>
     <hyperlink ref="J53" r:id="rId21" xr:uid="{24D0308A-22D0-4EA8-BF18-CB74A877A9ED}"/>
-    <hyperlink ref="J13" r:id="rId22" xr:uid="{07798078-5EF2-418B-926B-32B085A8EAB3}"/>
-    <hyperlink ref="J25" r:id="rId23" xr:uid="{6AD5C335-A479-4D1D-BE86-7C59DF0CAF54}"/>
-    <hyperlink ref="J23" r:id="rId24" xr:uid="{05668A5F-8025-48FA-BEE6-2CDC77003EDF}"/>
-    <hyperlink ref="J24" r:id="rId25" xr:uid="{5DE36C82-2916-4073-8BCB-B11CA92B4A85}"/>
-    <hyperlink ref="J20" r:id="rId26" xr:uid="{621916B0-703A-4ABD-836A-01E69D9F433B}"/>
-    <hyperlink ref="J26" r:id="rId27" xr:uid="{114EE048-6FD6-4606-B599-172DD13FA3F8}"/>
+    <hyperlink ref="J14" r:id="rId22" xr:uid="{07798078-5EF2-418B-926B-32B085A8EAB3}"/>
+    <hyperlink ref="J26" r:id="rId23" xr:uid="{6AD5C335-A479-4D1D-BE86-7C59DF0CAF54}"/>
+    <hyperlink ref="J24" r:id="rId24" xr:uid="{05668A5F-8025-48FA-BEE6-2CDC77003EDF}"/>
+    <hyperlink ref="J25" r:id="rId25" xr:uid="{5DE36C82-2916-4073-8BCB-B11CA92B4A85}"/>
+    <hyperlink ref="J21" r:id="rId26" xr:uid="{621916B0-703A-4ABD-836A-01E69D9F433B}"/>
+    <hyperlink ref="J27" r:id="rId27" xr:uid="{114EE048-6FD6-4606-B599-172DD13FA3F8}"/>
     <hyperlink ref="J66" r:id="rId28" xr:uid="{A4D718D4-6198-4FE8-B15E-10173BA491E8}"/>
     <hyperlink ref="J67" r:id="rId29" xr:uid="{F8B4AA82-7C18-466B-9A3F-52CC4EC9FEEF}"/>
     <hyperlink ref="J68" r:id="rId30" xr:uid="{903E7A31-2228-48A6-B9CE-D779283321E0}"/>
     <hyperlink ref="J32" r:id="rId31" xr:uid="{11E06CED-B5BE-4EE5-AD4E-A7DE1E24CB6F}"/>
     <hyperlink ref="J34" r:id="rId32" xr:uid="{950DA2AB-4F1A-4AF5-97E8-BE09B2A4CF7F}"/>
     <hyperlink ref="J35" r:id="rId33" xr:uid="{B1851711-0DAB-41CB-A077-003B128D248E}"/>
-    <hyperlink ref="J10" r:id="rId34" xr:uid="{68F08CBF-43FA-4141-9AD8-5D89AC72B358}"/>
-    <hyperlink ref="K12" r:id="rId35" xr:uid="{C2EEEAAD-E501-48FA-AA64-1A5F3B193710}"/>
+    <hyperlink ref="J11" r:id="rId34" xr:uid="{68F08CBF-43FA-4141-9AD8-5D89AC72B358}"/>
+    <hyperlink ref="K13" r:id="rId35" xr:uid="{C2EEEAAD-E501-48FA-AA64-1A5F3B193710}"/>
     <hyperlink ref="J45" r:id="rId36" xr:uid="{B1F324AE-5327-46E7-8281-E258EEC5109F}"/>
     <hyperlink ref="J61" r:id="rId37" xr:uid="{C5C341A3-7D12-45AC-9068-1F42F628D595}"/>
     <hyperlink ref="J59" r:id="rId38" xr:uid="{59B3973E-3E99-4A02-BA55-12D93D0FFCAF}"/>
     <hyperlink ref="J56" r:id="rId39" xr:uid="{F73B4C48-F126-4ABB-A25B-44CAB6EBCE08}"/>
-    <hyperlink ref="J22" r:id="rId40" xr:uid="{1ACD4BA2-51F9-4DBA-9CBC-10CB869FB5CF}"/>
+    <hyperlink ref="J23" r:id="rId40" xr:uid="{1ACD4BA2-51F9-4DBA-9CBC-10CB869FB5CF}"/>
     <hyperlink ref="J60" r:id="rId41" xr:uid="{F5F44425-0FC4-4561-9DB0-5367C1F085DC}"/>
     <hyperlink ref="J62" r:id="rId42" xr:uid="{6A6035A7-2DA9-400C-9CAC-A25336AAA7DA}"/>
-    <hyperlink ref="J12" r:id="rId43" xr:uid="{464DBC11-F2E4-4FF7-AFD0-D95603482D38}"/>
-    <hyperlink ref="J11" r:id="rId44" xr:uid="{4EE6AE69-2A48-468E-AA96-8013A302C145}"/>
-    <hyperlink ref="J9" r:id="rId45" xr:uid="{1B99D7DE-E976-4C33-9E1D-B70C9D1D8356}"/>
+    <hyperlink ref="J13" r:id="rId43" xr:uid="{464DBC11-F2E4-4FF7-AFD0-D95603482D38}"/>
+    <hyperlink ref="J12" r:id="rId44" xr:uid="{4EE6AE69-2A48-468E-AA96-8013A302C145}"/>
+    <hyperlink ref="J10" r:id="rId45" xr:uid="{1B99D7DE-E976-4C33-9E1D-B70C9D1D8356}"/>
     <hyperlink ref="J50" r:id="rId46" xr:uid="{AE9D1FE1-BE58-4174-8C84-96F3EEEB9F29}"/>
     <hyperlink ref="J71" r:id="rId47" xr:uid="{90DDBC3E-ABF8-4863-B731-02D735ED60A1}"/>
     <hyperlink ref="J72" r:id="rId48" xr:uid="{BBD202E7-6C40-4C9A-BC68-6C629F5863A5}"/>
     <hyperlink ref="J73" r:id="rId49" xr:uid="{DC4DA8CC-ECF9-4A4B-BC07-92BF171CDB99}"/>
     <hyperlink ref="J74" r:id="rId50" xr:uid="{05A0F23A-15E0-4E82-83B8-B0EAF8BEF4ED}"/>
     <hyperlink ref="J75" r:id="rId51" xr:uid="{56483B67-33AC-4EE2-AE3A-287085827DBF}"/>
-    <hyperlink ref="J17" r:id="rId52" xr:uid="{87309477-8CF1-4FC2-B823-390F8D78DF65}"/>
+    <hyperlink ref="J18" r:id="rId52" xr:uid="{87309477-8CF1-4FC2-B823-390F8D78DF65}"/>
     <hyperlink ref="J82" r:id="rId53" xr:uid="{D4C388B4-8E78-4F09-BBEE-DF7C93641240}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/open_trial_kit_parts.xlsx
+++ b/open_trial_kit_parts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Qiita\open_trial_kit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57350C7B-5CFB-4632-951C-70C96429BE7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9E67C2-A6B1-4104-9965-68510088D8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9870" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
+    <workbookView xWindow="-9060" yWindow="-21075" windowWidth="25635" windowHeight="18225" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="オープンハードウエア部材リスト" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="217">
   <si>
     <t>モーター</t>
     <phoneticPr fontId="3"/>
@@ -1094,17 +1094,41 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>価格は 2025/4 現在のものです</t>
+    <t>MVSHM-3N03000-456-YRTZX</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://meviy.misumi-ec.com/ja-jp/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00144816/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00139688/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00144801/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00134044/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00131331/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>価格は 2025/7 現在のものです</t>
     <rPh sb="0" eb="2">
       <t>カカク</t>
     </rPh>
     <rPh sb="11" eb="13">
       <t>ゲンザイ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>MVSHM-3N03000-456-YRTZX</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1384,7 +1408,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1496,6 +1520,12 @@
     <xf numFmtId="38" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1549,9 +1579,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1885,15 +1912,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="H1" s="55" t="s">
-        <v>209</v>
+      <c r="H1" s="37" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="44"/>
+      <c r="C2" s="46"/>
       <c r="D2" s="7" t="s">
         <v>16</v>
       </c>
@@ -1925,11 +1952,11 @@
       <c r="H3" s="22"/>
       <c r="I3" s="24">
         <f>SUM(I4:I8)</f>
-        <v>133740</v>
+        <v>132420</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="45"/>
+      <c r="B4" s="47"/>
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1952,9 +1979,12 @@
         <f>G4*H4</f>
         <v>55240</v>
       </c>
+      <c r="J4" s="9" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="46"/>
+      <c r="B5" s="48"/>
       <c r="C5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1977,9 +2007,12 @@
         <f t="shared" ref="I5:I8" si="0">G5*H5</f>
         <v>64260</v>
       </c>
+      <c r="J5" s="9" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="46"/>
+      <c r="B6" s="48"/>
       <c r="C6" s="5" t="s">
         <v>178</v>
       </c>
@@ -2002,9 +2035,12 @@
         <f t="shared" si="0"/>
         <v>5440</v>
       </c>
+      <c r="J6" s="9" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="46"/>
+      <c r="B7" s="48"/>
       <c r="C7" s="5" t="s">
         <v>6</v>
       </c>
@@ -2021,15 +2057,18 @@
         <v>2</v>
       </c>
       <c r="H7" s="6">
-        <v>2800</v>
+        <v>2380</v>
       </c>
       <c r="I7" s="20">
         <f t="shared" si="0"/>
-        <v>5600</v>
+        <v>4760</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="5" t="s">
         <v>8</v>
       </c>
@@ -2046,11 +2085,14 @@
         <v>2</v>
       </c>
       <c r="H8" s="6">
-        <v>1600</v>
+        <v>1360</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="0"/>
-        <v>3200</v>
+        <v>2720</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.4">
@@ -2065,11 +2107,11 @@
       <c r="H9" s="10"/>
       <c r="I9" s="25">
         <f>SUM(I10:I21)</f>
-        <v>38280</v>
+        <v>38520</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B10" s="48"/>
+      <c r="B10" s="50"/>
       <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
@@ -2086,18 +2128,18 @@
         <v>2</v>
       </c>
       <c r="H10" s="26">
-        <v>2490</v>
+        <v>2498</v>
       </c>
       <c r="I10" s="3">
         <f>G10*H10</f>
-        <v>4980</v>
+        <v>4996</v>
       </c>
       <c r="J10" s="32" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B11" s="48"/>
+      <c r="B11" s="50"/>
       <c r="C11" s="2" t="s">
         <v>13</v>
       </c>
@@ -2114,18 +2156,18 @@
         <v>1</v>
       </c>
       <c r="H11" s="3">
-        <v>14900</v>
+        <v>14980</v>
       </c>
       <c r="I11" s="3">
         <f t="shared" ref="I11:I21" si="1">G11*H11</f>
-        <v>14900</v>
+        <v>14980</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B12" s="48"/>
+      <c r="B12" s="50"/>
       <c r="C12" s="2" t="s">
         <v>125</v>
       </c>
@@ -2153,7 +2195,7 @@
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B13" s="48"/>
+      <c r="B13" s="50"/>
       <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
@@ -2184,7 +2226,7 @@
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B14" s="48"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="2" t="s">
         <v>29</v>
       </c>
@@ -2201,18 +2243,18 @@
         <v>1</v>
       </c>
       <c r="H14" s="3">
-        <v>6312</v>
+        <v>6020</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="1"/>
-        <v>6312</v>
+        <v>6020</v>
       </c>
       <c r="J14" s="15" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B15" s="48"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
@@ -2238,7 +2280,7 @@
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B16" s="48"/>
+      <c r="B16" s="50"/>
       <c r="C16" s="2" t="s">
         <v>35</v>
       </c>
@@ -2266,7 +2308,7 @@
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="48"/>
+      <c r="B17" s="50"/>
       <c r="C17" s="2" t="s">
         <v>40</v>
       </c>
@@ -2283,18 +2325,18 @@
         <v>1</v>
       </c>
       <c r="H17" s="3">
-        <v>2337</v>
+        <v>2720</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="1"/>
-        <v>2337</v>
+        <v>2720</v>
       </c>
       <c r="J17" s="18" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="48"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="2" t="s">
         <v>195</v>
       </c>
@@ -2311,18 +2353,18 @@
         <v>1</v>
       </c>
       <c r="H18" s="3">
-        <v>1599</v>
+        <v>1636</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="1"/>
-        <v>1599</v>
+        <v>1636</v>
       </c>
       <c r="J18" s="18" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="48"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="2" t="s">
         <v>44</v>
       </c>
@@ -2339,18 +2381,18 @@
         <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="1"/>
-        <v>1690</v>
+        <v>1698</v>
       </c>
       <c r="J19" s="18" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="48"/>
+      <c r="B20" s="50"/>
       <c r="C20" s="2" t="s">
         <v>47</v>
       </c>
@@ -2378,7 +2420,7 @@
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="48"/>
+      <c r="B21" s="50"/>
       <c r="C21" s="2" t="s">
         <v>52</v>
       </c>
@@ -2395,11 +2437,11 @@
         <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="1"/>
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="J21" s="18" t="s">
         <v>188</v>
@@ -2417,11 +2459,11 @@
       <c r="H22" s="22"/>
       <c r="I22" s="24">
         <f>SUM(I23:I27)</f>
-        <v>4187</v>
+        <v>4230</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="49"/>
+      <c r="B23" s="51"/>
       <c r="C23" s="5" t="s">
         <v>99</v>
       </c>
@@ -2437,19 +2479,19 @@
       <c r="G23" s="5">
         <v>1</v>
       </c>
-      <c r="H23" s="5">
-        <v>2925</v>
+      <c r="H23" s="38">
+        <v>2968</v>
       </c>
       <c r="I23" s="6">
         <f>G23*H23</f>
-        <v>2925</v>
+        <v>2968</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="50"/>
+      <c r="B24" s="52"/>
       <c r="C24" s="5" t="s">
         <v>51</v>
       </c>
@@ -2477,7 +2519,7 @@
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="50"/>
+      <c r="B25" s="52"/>
       <c r="C25" s="5" t="s">
         <v>102</v>
       </c>
@@ -2505,7 +2547,7 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="50"/>
+      <c r="B26" s="52"/>
       <c r="C26" s="5" t="s">
         <v>100</v>
       </c>
@@ -2533,7 +2575,7 @@
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="51"/>
+      <c r="B27" s="53"/>
       <c r="C27" s="5" t="s">
         <v>100</v>
       </c>
@@ -2572,7 +2614,7 @@
       <c r="H28" s="10"/>
       <c r="I28" s="25">
         <f>SUM(I29)</f>
-        <v>29568</v>
+        <v>28944</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.4">
@@ -2591,11 +2633,11 @@
         <v>1</v>
       </c>
       <c r="H29" s="26">
-        <v>29568</v>
+        <v>28944</v>
       </c>
       <c r="I29" s="16">
         <f>G29*H29</f>
-        <v>29568</v>
+        <v>28944</v>
       </c>
       <c r="J29" s="17" t="s">
         <v>32</v>
@@ -2613,11 +2655,11 @@
       <c r="H30" s="22"/>
       <c r="I30" s="24">
         <f>SUM(I31:I35)</f>
-        <v>47632</v>
+        <v>51032</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="45"/>
+      <c r="B31" s="47"/>
       <c r="C31" s="5" t="s">
         <v>39</v>
       </c>
@@ -2640,9 +2682,12 @@
         <f t="shared" ref="I31:I35" si="3">G31*H31</f>
         <v>30868</v>
       </c>
+      <c r="J31" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="46"/>
+      <c r="B32" s="48"/>
       <c r="C32" s="5" t="s">
         <v>55</v>
       </c>
@@ -2670,7 +2715,7 @@
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="46"/>
+      <c r="B33" s="48"/>
       <c r="C33" s="5" t="s">
         <v>152</v>
       </c>
@@ -2698,7 +2743,7 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="46"/>
+      <c r="B34" s="48"/>
       <c r="C34" s="5" t="s">
         <v>57</v>
       </c>
@@ -2726,7 +2771,7 @@
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="47"/>
+      <c r="B35" s="49"/>
       <c r="C35" s="5" t="s">
         <v>21</v>
       </c>
@@ -2743,11 +2788,11 @@
         <v>2</v>
       </c>
       <c r="H35" s="6">
-        <v>2326</v>
+        <v>4026</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
-        <v>4652</v>
+        <v>8052</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>150</v>
@@ -2765,11 +2810,11 @@
       <c r="H36" s="10"/>
       <c r="I36" s="25">
         <f>SUM(I37:I68)</f>
-        <v>70777</v>
+        <v>74933</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="52"/>
+      <c r="B37" s="54"/>
       <c r="C37" s="2" t="s">
         <v>95</v>
       </c>
@@ -2792,9 +2837,12 @@
         <f>G37*H37</f>
         <v>10832</v>
       </c>
+      <c r="J37" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="53"/>
+      <c r="B38" s="55"/>
       <c r="C38" s="2" t="s">
         <v>141</v>
       </c>
@@ -2817,9 +2865,12 @@
         <f t="shared" ref="I38:I68" si="4">G38*H38</f>
         <v>5842</v>
       </c>
+      <c r="J38" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="53"/>
+      <c r="B39" s="55"/>
       <c r="C39" s="2" t="s">
         <v>54</v>
       </c>
@@ -2836,15 +2887,18 @@
         <v>1</v>
       </c>
       <c r="H39" s="3">
-        <v>8629</v>
+        <v>9406</v>
       </c>
       <c r="I39" s="3">
         <f t="shared" si="4"/>
-        <v>8629</v>
+        <v>9406</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="53"/>
+      <c r="B40" s="55"/>
       <c r="C40" s="2" t="s">
         <v>174</v>
       </c>
@@ -2867,9 +2921,12 @@
         <f t="shared" si="4"/>
         <v>3268</v>
       </c>
+      <c r="J40" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="53"/>
+      <c r="B41" s="55"/>
       <c r="C41" s="2" t="s">
         <v>181</v>
       </c>
@@ -2877,7 +2934,7 @@
         <v>53</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
@@ -2892,9 +2949,12 @@
         <f t="shared" si="4"/>
         <v>2424</v>
       </c>
+      <c r="J41" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="53"/>
+      <c r="B42" s="55"/>
       <c r="C42" s="2" t="s">
         <v>179</v>
       </c>
@@ -2917,9 +2977,12 @@
         <f t="shared" si="4"/>
         <v>2527</v>
       </c>
+      <c r="J42" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="53"/>
+      <c r="B43" s="55"/>
       <c r="C43" s="2" t="s">
         <v>175</v>
       </c>
@@ -2936,15 +2999,18 @@
         <v>2</v>
       </c>
       <c r="H43" s="3">
-        <v>3408</v>
+        <v>4005</v>
       </c>
       <c r="I43" s="3">
         <f t="shared" si="4"/>
-        <v>6816</v>
+        <v>8010</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="53"/>
+      <c r="B44" s="55"/>
       <c r="C44" s="2" t="s">
         <v>175</v>
       </c>
@@ -2961,15 +3027,18 @@
         <v>2</v>
       </c>
       <c r="H44" s="3">
-        <v>2706</v>
+        <v>3180</v>
       </c>
       <c r="I44" s="3">
         <f t="shared" si="4"/>
-        <v>5412</v>
+        <v>6360</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="53"/>
+      <c r="B45" s="55"/>
       <c r="C45" s="2" t="s">
         <v>140</v>
       </c>
@@ -2997,7 +3066,7 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="53"/>
+      <c r="B46" s="55"/>
       <c r="C46" s="2" t="s">
         <v>59</v>
       </c>
@@ -3025,7 +3094,7 @@
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="53"/>
+      <c r="B47" s="55"/>
       <c r="C47" s="2" t="s">
         <v>64</v>
       </c>
@@ -3053,7 +3122,7 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="53"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="2" t="s">
         <v>65</v>
       </c>
@@ -3081,7 +3150,7 @@
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="53"/>
+      <c r="B49" s="55"/>
       <c r="C49" s="2" t="s">
         <v>66</v>
       </c>
@@ -3109,7 +3178,7 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="53"/>
+      <c r="B50" s="55"/>
       <c r="C50" s="2" t="s">
         <v>67</v>
       </c>
@@ -3137,7 +3206,7 @@
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="53"/>
+      <c r="B51" s="55"/>
       <c r="C51" s="2" t="s">
         <v>79</v>
       </c>
@@ -3165,7 +3234,7 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="53"/>
+      <c r="B52" s="55"/>
       <c r="C52" s="2" t="s">
         <v>62</v>
       </c>
@@ -3193,7 +3262,7 @@
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="53"/>
+      <c r="B53" s="55"/>
       <c r="C53" s="2" t="s">
         <v>63</v>
       </c>
@@ -3221,7 +3290,7 @@
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="53"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="2" t="s">
         <v>159</v>
       </c>
@@ -3238,18 +3307,18 @@
         <v>1</v>
       </c>
       <c r="H54" s="3">
-        <v>792</v>
+        <v>897</v>
       </c>
       <c r="I54" s="3">
         <f t="shared" si="4"/>
-        <v>792</v>
+        <v>897</v>
       </c>
       <c r="J54" s="9" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="53"/>
+      <c r="B55" s="55"/>
       <c r="C55" s="2" t="s">
         <v>76</v>
       </c>
@@ -3266,18 +3335,18 @@
         <v>10</v>
       </c>
       <c r="H55" s="3">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="I55" s="3">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>580</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="53"/>
+      <c r="B56" s="55"/>
       <c r="C56" s="2" t="s">
         <v>135</v>
       </c>
@@ -3305,7 +3374,7 @@
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="53"/>
+      <c r="B57" s="55"/>
       <c r="C57" s="2" t="s">
         <v>74</v>
       </c>
@@ -3333,7 +3402,7 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="53"/>
+      <c r="B58" s="55"/>
       <c r="C58" s="2" t="s">
         <v>69</v>
       </c>
@@ -3350,18 +3419,18 @@
         <v>28</v>
       </c>
       <c r="H58" s="3">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="I58" s="3">
         <f t="shared" si="4"/>
-        <v>952</v>
+        <v>1652</v>
       </c>
       <c r="J58" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="53"/>
+      <c r="B59" s="55"/>
       <c r="C59" s="2" t="s">
         <v>132</v>
       </c>
@@ -3378,18 +3447,18 @@
         <v>10</v>
       </c>
       <c r="H59" s="3">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="I59" s="3">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>590</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="53"/>
+      <c r="B60" s="55"/>
       <c r="C60" s="2" t="s">
         <v>142</v>
       </c>
@@ -3417,7 +3486,7 @@
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="53"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="2" t="s">
         <v>129</v>
       </c>
@@ -3445,7 +3514,7 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="53"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="2" t="s">
         <v>145</v>
       </c>
@@ -3473,7 +3542,7 @@
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="53"/>
+      <c r="B63" s="55"/>
       <c r="C63" s="2" t="s">
         <v>164</v>
       </c>
@@ -3501,7 +3570,7 @@
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="53"/>
+      <c r="B64" s="55"/>
       <c r="C64" s="2" t="s">
         <v>162</v>
       </c>
@@ -3530,7 +3599,7 @@
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B65" s="53"/>
+      <c r="B65" s="55"/>
       <c r="C65" s="2" t="s">
         <v>94</v>
       </c>
@@ -3558,7 +3627,7 @@
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B66" s="53"/>
+      <c r="B66" s="55"/>
       <c r="C66" s="2" t="s">
         <v>89</v>
       </c>
@@ -3586,7 +3655,7 @@
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B67" s="53"/>
+      <c r="B67" s="55"/>
       <c r="C67" s="2" t="s">
         <v>90</v>
       </c>
@@ -3603,18 +3672,18 @@
         <v>2</v>
       </c>
       <c r="H67" s="3">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="I67" s="3">
         <f t="shared" si="4"/>
-        <v>478</v>
+        <v>460</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B68" s="54"/>
+      <c r="B68" s="56"/>
       <c r="C68" s="2" t="s">
         <v>92</v>
       </c>
@@ -3653,11 +3722,11 @@
       <c r="H69" s="22"/>
       <c r="I69" s="24">
         <f>SUM(I70:I75)</f>
-        <v>10203</v>
+        <v>10509</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B70" s="45"/>
+      <c r="B70" s="47"/>
       <c r="C70" s="5" t="s">
         <v>182</v>
       </c>
@@ -3680,9 +3749,12 @@
         <f>G70*H70</f>
         <v>7635</v>
       </c>
+      <c r="J70" s="9" t="s">
+        <v>210</v>
+      </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B71" s="46"/>
+      <c r="B71" s="48"/>
       <c r="C71" s="5" t="s">
         <v>184</v>
       </c>
@@ -3710,7 +3782,7 @@
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B72" s="46"/>
+      <c r="B72" s="48"/>
       <c r="C72" s="5" t="s">
         <v>186</v>
       </c>
@@ -3738,7 +3810,7 @@
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B73" s="46"/>
+      <c r="B73" s="48"/>
       <c r="C73" s="5" t="s">
         <v>162</v>
       </c>
@@ -3766,7 +3838,7 @@
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B74" s="46"/>
+      <c r="B74" s="48"/>
       <c r="C74" s="5" t="s">
         <v>69</v>
       </c>
@@ -3783,18 +3855,18 @@
         <v>6</v>
       </c>
       <c r="H74" s="6">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="5"/>
-        <v>204</v>
+        <v>510</v>
       </c>
       <c r="J74" s="9" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B75" s="47"/>
+      <c r="B75" s="49"/>
       <c r="C75" s="5" t="s">
         <v>63</v>
       </c>
@@ -3832,18 +3904,18 @@
       <c r="I76" s="12"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B77" s="41" t="s">
+      <c r="B77" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="C77" s="42"/>
-      <c r="D77" s="42"/>
-      <c r="E77" s="42"/>
-      <c r="F77" s="43"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="45"/>
       <c r="G77" s="31"/>
       <c r="H77" s="14"/>
       <c r="I77" s="14">
         <f>I3+I9+I22+I28+I30+I36+I69</f>
-        <v>334387</v>
+        <v>340588</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.4">
@@ -3852,10 +3924,10 @@
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B80" s="39" t="s">
+      <c r="B80" s="41" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="40"/>
+      <c r="C80" s="42"/>
       <c r="D80" s="35"/>
       <c r="E80" s="35"/>
       <c r="F80" s="35"/>
@@ -3864,7 +3936,7 @@
       <c r="I80" s="36"/>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B81" s="37"/>
+      <c r="B81" s="39"/>
       <c r="C81" s="2" t="s">
         <v>200</v>
       </c>
@@ -3884,7 +3956,7 @@
       <c r="I81" s="3"/>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B82" s="38"/>
+      <c r="B82" s="40"/>
       <c r="C82" s="2" t="s">
         <v>203</v>
       </c>
@@ -3974,8 +4046,16 @@
     <hyperlink ref="J75" r:id="rId51" xr:uid="{56483B67-33AC-4EE2-AE3A-287085827DBF}"/>
     <hyperlink ref="J18" r:id="rId52" xr:uid="{87309477-8CF1-4FC2-B823-390F8D78DF65}"/>
     <hyperlink ref="J82" r:id="rId53" xr:uid="{D4C388B4-8E78-4F09-BBEE-DF7C93641240}"/>
+    <hyperlink ref="J31" r:id="rId54" xr:uid="{5B24EF0F-C6A4-47E1-8CC7-ED00C25C7AC3}"/>
+    <hyperlink ref="J37:J44" r:id="rId55" display="https://meviy.misumi-ec.com/ja-jp/" xr:uid="{FDBD395D-3BD0-48FC-B50D-2052192C0F1C}"/>
+    <hyperlink ref="J70" r:id="rId56" xr:uid="{4E136A16-60EE-456F-85D3-252B93C80D51}"/>
+    <hyperlink ref="J4" r:id="rId57" xr:uid="{272C059B-1D1E-4FA7-9A73-EBA0704A055E}"/>
+    <hyperlink ref="J5" r:id="rId58" xr:uid="{0DCA6E50-1A77-4787-BDAF-E2F530E5F5A5}"/>
+    <hyperlink ref="J6" r:id="rId59" xr:uid="{CBAC2EE7-F2BC-4255-BA66-1B704B3DA056}"/>
+    <hyperlink ref="J7" r:id="rId60" xr:uid="{28FFAE5B-B7BE-42FD-BCA4-4EE6B32AA1E9}"/>
+    <hyperlink ref="J8" r:id="rId61" xr:uid="{99EA8925-0994-41B9-BC80-375EA21AA671}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId54"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId62"/>
 </worksheet>
 </file>
--- a/open_trial_kit_parts.xlsx
+++ b/open_trial_kit_parts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\Qiita\open_trial_kit\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\atmobi\open_trial_kit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E9E67C2-A6B1-4104-9965-68510088D8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554F2246-EC16-480D-9092-C602C99F7E97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-9060" yWindow="-21075" windowWidth="25635" windowHeight="18225" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
+    <workbookView xWindow="28680" yWindow="-6060" windowWidth="38640" windowHeight="23520" xr2:uid="{324A818F-9097-425C-8F87-08D4E2539DA0}"/>
   </bookViews>
   <sheets>
     <sheet name="オープンハードウエア部材リスト" sheetId="5" r:id="rId1"/>
@@ -36,17 +36,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="220">
   <si>
     <t>モーター</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
     <t xml:space="preserve">ブラシレスモーター </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>BLMR460SHK-15</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1102,10 +1098,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>https://www.orimvexta.co.jp/shop/item/detail/00144816/</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>https://www.orimvexta.co.jp/shop/item/detail/00139688/</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -1129,6 +1121,26 @@
     <rPh sb="11" eb="13">
       <t>ゲンザイ</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>BLMR460SHK-GFV</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>ギヤヘッド</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>GFV4G15</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00144838/</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>https://www.orimvexta.co.jp/shop/item/detail/00136830/</t>
     <phoneticPr fontId="3"/>
   </si>
 </sst>
@@ -1898,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EB10439-63C0-489A-BA2E-F544E29F3044}">
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="5.375" customWidth="1"/>
@@ -1913,31 +1925,31 @@
   <sheetData>
     <row r="1" spans="2:11" x14ac:dyDescent="0.4">
       <c r="H1" s="37" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" s="46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="46"/>
       <c r="D2" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
@@ -1951,8 +1963,8 @@
       <c r="G3" s="22"/>
       <c r="H3" s="22"/>
       <c r="I3" s="24">
-        <f>SUM(I4:I8)</f>
-        <v>132420</v>
+        <f>SUM(I4:I9)</f>
+        <v>142180</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
@@ -1961,10 +1973,10 @@
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>2</v>
+        <v>215</v>
       </c>
       <c r="F4" s="5">
         <v>2</v>
@@ -1973,26 +1985,26 @@
         <v>2</v>
       </c>
       <c r="H4" s="6">
-        <v>27620</v>
+        <v>21000</v>
       </c>
       <c r="I4" s="20">
         <f>G4*H4</f>
-        <v>55240</v>
+        <v>42000</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="48"/>
       <c r="C5" s="5" t="s">
-        <v>3</v>
+        <v>216</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>4</v>
+        <v>217</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
@@ -2001,26 +2013,26 @@
         <v>2</v>
       </c>
       <c r="H5" s="6">
-        <v>32130</v>
+        <v>11500</v>
       </c>
       <c r="I5" s="20">
-        <f t="shared" ref="I5:I8" si="0">G5*H5</f>
-        <v>64260</v>
+        <f>G5*H5</f>
+        <v>23000</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="48"/>
       <c r="C6" s="5" t="s">
-        <v>178</v>
+        <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5">
         <v>2</v>
@@ -2029,26 +2041,26 @@
         <v>2</v>
       </c>
       <c r="H6" s="6">
-        <v>2720</v>
+        <v>32130</v>
       </c>
       <c r="I6" s="20">
-        <f t="shared" si="0"/>
-        <v>5440</v>
+        <f t="shared" ref="I6:I9" si="0">G6*H6</f>
+        <v>64260</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="48"/>
       <c r="C7" s="5" t="s">
-        <v>6</v>
+        <v>177</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F7" s="5">
         <v>2</v>
@@ -2057,26 +2069,26 @@
         <v>2</v>
       </c>
       <c r="H7" s="6">
-        <v>2380</v>
+        <v>2720</v>
       </c>
       <c r="I7" s="20">
         <f t="shared" si="0"/>
-        <v>4760</v>
+        <v>5440</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="49"/>
+      <c r="B8" s="48"/>
       <c r="C8" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F8" s="5">
         <v>2</v>
@@ -2085,97 +2097,97 @@
         <v>2</v>
       </c>
       <c r="H8" s="6">
-        <v>1360</v>
+        <v>2380</v>
       </c>
       <c r="I8" s="20">
         <f t="shared" si="0"/>
+        <v>4760</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B9" s="49"/>
+      <c r="C9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2</v>
+      </c>
+      <c r="G9" s="5">
+        <v>2</v>
+      </c>
+      <c r="H9" s="6">
+        <v>1360</v>
+      </c>
+      <c r="I9" s="20">
+        <f t="shared" si="0"/>
         <v>2720</v>
       </c>
-      <c r="J8" s="9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="25">
-        <f>SUM(I10:I21)</f>
+      <c r="J9" s="9" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B10" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="25">
+        <f>SUM(I11:I22)</f>
         <v>38520</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B10" s="50"/>
-      <c r="C10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="2">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>2</v>
-      </c>
-      <c r="H10" s="26">
-        <v>2498</v>
-      </c>
-      <c r="I10" s="3">
-        <f>G10*H10</f>
-        <v>4996</v>
-      </c>
-      <c r="J10" s="32" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="50"/>
       <c r="C11" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3">
-        <v>14980</v>
+        <v>2</v>
+      </c>
+      <c r="H11" s="26">
+        <v>2498</v>
       </c>
       <c r="I11" s="3">
-        <f t="shared" ref="I11:I21" si="1">G11*H11</f>
-        <v>14980</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>120</v>
+        <f>G11*H11</f>
+        <v>4996</v>
+      </c>
+      <c r="J11" s="32" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="50"/>
       <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F12" s="2">
         <v>1</v>
@@ -2184,26 +2196,26 @@
         <v>1</v>
       </c>
       <c r="H12" s="3">
-        <v>2172</v>
+        <v>14980</v>
       </c>
       <c r="I12" s="3">
-        <f t="shared" si="1"/>
-        <v>2172</v>
+        <f t="shared" ref="I12:I22" si="1">G12*H12</f>
+        <v>14980</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="50"/>
       <c r="C13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F13" s="2">
         <v>1</v>
@@ -2212,29 +2224,26 @@
         <v>1</v>
       </c>
       <c r="H13" s="3">
-        <v>1600</v>
+        <v>2172</v>
       </c>
       <c r="I13" s="3">
         <f t="shared" si="1"/>
-        <v>1600</v>
+        <v>2172</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>154</v>
-      </c>
-      <c r="K13" s="9" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="50"/>
       <c r="C14" s="2" t="s">
-        <v>29</v>
+        <v>124</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="F14" s="2">
         <v>1</v>
@@ -2243,25 +2252,30 @@
         <v>1</v>
       </c>
       <c r="H14" s="3">
-        <v>6020</v>
+        <v>1600</v>
       </c>
       <c r="I14" s="3">
         <f t="shared" si="1"/>
-        <v>6020</v>
-      </c>
-      <c r="J14" s="15" t="s">
-        <v>96</v>
+        <v>1600</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B15" s="50"/>
       <c r="C15" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="F15" s="2">
         <v>1</v>
       </c>
@@ -2269,27 +2283,25 @@
         <v>1</v>
       </c>
       <c r="H15" s="3">
-        <v>695</v>
+        <v>6020</v>
       </c>
       <c r="I15" s="3">
         <f t="shared" si="1"/>
-        <v>695</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>34</v>
+        <v>6020</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B16" s="50"/>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>37</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="E16" s="2"/>
       <c r="F16" s="2">
         <v>1</v>
       </c>
@@ -2297,26 +2309,26 @@
         <v>1</v>
       </c>
       <c r="H16" s="3">
-        <v>1540</v>
+        <v>695</v>
       </c>
       <c r="I16" s="3">
         <f t="shared" si="1"/>
-        <v>1540</v>
+        <v>695</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B17" s="50"/>
       <c r="C17" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F17" s="2">
         <v>1</v>
@@ -2325,26 +2337,26 @@
         <v>1</v>
       </c>
       <c r="H17" s="3">
-        <v>2720</v>
+        <v>1540</v>
       </c>
       <c r="I17" s="3">
         <f t="shared" si="1"/>
-        <v>2720</v>
+        <v>1540</v>
       </c>
       <c r="J17" s="18" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B18" s="50"/>
       <c r="C18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>196</v>
+        <v>39</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="F18" s="2">
         <v>1</v>
@@ -2353,26 +2365,26 @@
         <v>1</v>
       </c>
       <c r="H18" s="3">
-        <v>1636</v>
+        <v>2720</v>
       </c>
       <c r="I18" s="3">
         <f t="shared" si="1"/>
-        <v>1636</v>
+        <v>2720</v>
       </c>
       <c r="J18" s="18" t="s">
-        <v>197</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="50"/>
       <c r="C19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>45</v>
+        <v>194</v>
+      </c>
+      <c r="D19" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E19" s="30" t="s">
+        <v>195</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
@@ -2381,26 +2393,26 @@
         <v>1</v>
       </c>
       <c r="H19" s="3">
-        <v>1698</v>
+        <v>1636</v>
       </c>
       <c r="I19" s="3">
         <f t="shared" si="1"/>
-        <v>1698</v>
+        <v>1636</v>
       </c>
       <c r="J19" s="18" t="s">
-        <v>46</v>
+        <v>196</v>
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B20" s="50"/>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
@@ -2409,26 +2421,26 @@
         <v>1</v>
       </c>
       <c r="H20" s="3">
-        <v>229</v>
+        <v>1698</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="1"/>
-        <v>229</v>
+        <v>1698</v>
       </c>
       <c r="J20" s="18" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B21" s="50"/>
       <c r="C21" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="F21" s="2">
         <v>1</v>
@@ -2437,293 +2449,293 @@
         <v>1</v>
       </c>
       <c r="H21" s="3">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="I21" s="3">
         <f t="shared" si="1"/>
+        <v>229</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B22" s="50"/>
+      <c r="C22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
         <v>234</v>
       </c>
-      <c r="J21" s="18" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="21" t="s">
+      <c r="I22" s="3">
+        <f t="shared" si="1"/>
+        <v>234</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B23" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="24">
+        <f>SUM(I24:I28)</f>
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B24" s="51"/>
+      <c r="C24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="24">
-        <f>SUM(I23:I27)</f>
-        <v>4230</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="51"/>
-      <c r="C23" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
-      <c r="G23" s="5">
-        <v>1</v>
-      </c>
-      <c r="H23" s="38">
+      <c r="E24" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F24" s="5">
+        <v>1</v>
+      </c>
+      <c r="G24" s="5">
+        <v>1</v>
+      </c>
+      <c r="H24" s="38">
         <v>2968</v>
       </c>
-      <c r="I23" s="6">
-        <f>G23*H23</f>
+      <c r="I24" s="6">
+        <f>G24*H24</f>
         <v>2968</v>
       </c>
-      <c r="J23" s="9" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="52"/>
-      <c r="C24" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="F24" s="5">
-        <v>5</v>
-      </c>
-      <c r="G24" s="5">
-        <v>5</v>
-      </c>
-      <c r="H24" s="6">
-        <v>96</v>
-      </c>
-      <c r="I24" s="6">
-        <f t="shared" ref="I24:I27" si="2">G24*H24</f>
-        <v>480</v>
-      </c>
       <c r="J24" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B25" s="52"/>
       <c r="C25" s="5" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F25" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G25" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H25" s="6">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="I25" s="6">
-        <f t="shared" si="2"/>
-        <v>108</v>
+        <f t="shared" ref="I25:I28" si="2">G25*H25</f>
+        <v>480</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B26" s="52"/>
       <c r="C26" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="E26" s="28" t="s">
-        <v>108</v>
+        <v>82</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>102</v>
       </c>
       <c r="F26" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="I26" s="6">
         <f t="shared" si="2"/>
-        <v>396</v>
+        <v>108</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="53"/>
+      <c r="B27" s="52"/>
       <c r="C27" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F27" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="6">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="I27" s="6">
         <f t="shared" si="2"/>
+        <v>396</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B28" s="53"/>
+      <c r="C28" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="F28" s="5">
+        <v>2</v>
+      </c>
+      <c r="G28" s="5">
+        <v>2</v>
+      </c>
+      <c r="H28" s="6">
+        <v>139</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="2"/>
         <v>278</v>
       </c>
-      <c r="J27" s="9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="19" t="s">
+      <c r="J28" s="9" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B29" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="25">
+        <f>SUM(I30)</f>
+        <v>28944</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B30" s="23"/>
+      <c r="C30" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="25">
-        <f>SUM(I29)</f>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="26">
         <v>28944</v>
       </c>
-    </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="23"/>
-      <c r="C29" s="2" t="s">
+      <c r="I30" s="16">
+        <f>G30*H30</f>
+        <v>28944</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B31" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="2">
-        <v>1</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="H29" s="26">
-        <v>28944</v>
-      </c>
-      <c r="I29" s="16">
-        <f>G29*H29</f>
-        <v>28944</v>
-      </c>
-      <c r="J29" s="17" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="24">
-        <f>SUM(I31:I35)</f>
+      <c r="C31" s="22"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="24">
+        <f>SUM(I32:I36)</f>
         <v>51032</v>
       </c>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="47"/>
-      <c r="C31" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="F31" s="5">
-        <v>2</v>
-      </c>
-      <c r="G31" s="5">
-        <v>2</v>
-      </c>
-      <c r="H31" s="6">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B32" s="47"/>
+      <c r="C32" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2</v>
+      </c>
+      <c r="G32" s="5">
+        <v>2</v>
+      </c>
+      <c r="H32" s="6">
         <v>15434</v>
       </c>
-      <c r="I31" s="6">
-        <f t="shared" ref="I31:I35" si="3">G31*H31</f>
+      <c r="I32" s="6">
+        <f t="shared" ref="I32:I36" si="3">G32*H32</f>
         <v>30868</v>
       </c>
-      <c r="J31" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="48"/>
-      <c r="C32" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" s="5">
-        <v>2</v>
-      </c>
-      <c r="G32" s="5">
-        <v>2</v>
-      </c>
-      <c r="H32" s="6">
-        <v>510</v>
-      </c>
-      <c r="I32" s="6">
-        <f t="shared" si="3"/>
-        <v>1020</v>
-      </c>
       <c r="J32" s="9" t="s">
-        <v>117</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B33" s="48"/>
       <c r="C33" s="5" t="s">
-        <v>152</v>
+        <v>54</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="F33" s="5">
         <v>2</v>
@@ -2732,26 +2744,26 @@
         <v>2</v>
       </c>
       <c r="H33" s="6">
-        <v>5510</v>
+        <v>510</v>
       </c>
       <c r="I33" s="6">
         <f t="shared" si="3"/>
-        <v>11020</v>
+        <v>1020</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>153</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B34" s="48"/>
       <c r="C34" s="5" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>58</v>
+        <v>150</v>
       </c>
       <c r="F34" s="5">
         <v>2</v>
@@ -2760,26 +2772,26 @@
         <v>2</v>
       </c>
       <c r="H34" s="6">
-        <v>36</v>
+        <v>5510</v>
       </c>
       <c r="I34" s="6">
         <f t="shared" si="3"/>
-        <v>72</v>
+        <v>11020</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="49"/>
+      <c r="B35" s="48"/>
       <c r="C35" s="5" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="F35" s="5">
         <v>2</v>
@@ -2788,66 +2800,66 @@
         <v>2</v>
       </c>
       <c r="H35" s="6">
-        <v>4026</v>
+        <v>36</v>
       </c>
       <c r="I35" s="6">
         <f t="shared" si="3"/>
+        <v>72</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B36" s="49"/>
+      <c r="C36" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" s="5">
+        <v>2</v>
+      </c>
+      <c r="G36" s="5">
+        <v>2</v>
+      </c>
+      <c r="H36" s="6">
+        <v>4026</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="3"/>
         <v>8052</v>
       </c>
-      <c r="J35" s="9" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="25">
-        <f>SUM(I37:I68)</f>
+      <c r="J36" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B37" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="10"/>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="25">
+        <f>SUM(I38:I69)</f>
         <v>74933</v>
       </c>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="54"/>
-      <c r="C37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="2">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3">
-        <v>10832</v>
-      </c>
-      <c r="I37" s="3">
-        <f>G37*H37</f>
-        <v>10832</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="55"/>
+      <c r="B38" s="54"/>
       <c r="C38" s="2" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>112</v>
@@ -2858,27 +2870,27 @@
       <c r="G38" s="2">
         <v>1</v>
       </c>
-      <c r="H38" s="27">
-        <v>5842</v>
+      <c r="H38" s="3">
+        <v>10832</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" ref="I38:I68" si="4">G38*H38</f>
-        <v>5842</v>
+        <f>G38*H38</f>
+        <v>10832</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B39" s="55"/>
       <c r="C39" s="2" t="s">
-        <v>54</v>
+        <v>140</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="F39" s="2">
         <v>1</v>
@@ -2886,27 +2898,27 @@
       <c r="G39" s="2">
         <v>1</v>
       </c>
-      <c r="H39" s="3">
-        <v>9406</v>
+      <c r="H39" s="27">
+        <v>5842</v>
       </c>
       <c r="I39" s="3">
-        <f t="shared" si="4"/>
-        <v>9406</v>
+        <f t="shared" ref="I39:I69" si="4">G39*H39</f>
+        <v>5842</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B40" s="55"/>
       <c r="C40" s="2" t="s">
-        <v>174</v>
+        <v>53</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>173</v>
+        <v>147</v>
       </c>
       <c r="F40" s="2">
         <v>1</v>
@@ -2915,26 +2927,26 @@
         <v>1</v>
       </c>
       <c r="H40" s="3">
-        <v>3268</v>
+        <v>9406</v>
       </c>
       <c r="I40" s="3">
         <f t="shared" si="4"/>
-        <v>3268</v>
+        <v>9406</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B41" s="55"/>
       <c r="C41" s="2" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>209</v>
+        <v>172</v>
       </c>
       <c r="F41" s="2">
         <v>1</v>
@@ -2943,26 +2955,26 @@
         <v>1</v>
       </c>
       <c r="H41" s="3">
-        <v>2424</v>
+        <v>3268</v>
       </c>
       <c r="I41" s="3">
         <f t="shared" si="4"/>
-        <v>2424</v>
+        <v>3268</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B42" s="55"/>
       <c r="C42" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>180</v>
+        <v>208</v>
       </c>
       <c r="F42" s="2">
         <v>1</v>
@@ -2971,55 +2983,55 @@
         <v>1</v>
       </c>
       <c r="H42" s="3">
-        <v>2527</v>
+        <v>2424</v>
       </c>
       <c r="I42" s="3">
         <f t="shared" si="4"/>
-        <v>2527</v>
+        <v>2424</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B43" s="55"/>
       <c r="C43" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3">
-        <v>4005</v>
+        <v>2527</v>
       </c>
       <c r="I43" s="3">
         <f t="shared" si="4"/>
-        <v>8010</v>
+        <v>2527</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B44" s="55"/>
       <c r="C44" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D44" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="F44" s="2">
         <v>2</v>
       </c>
@@ -3027,26 +3039,26 @@
         <v>2</v>
       </c>
       <c r="H44" s="3">
-        <v>3180</v>
+        <v>4005</v>
       </c>
       <c r="I44" s="3">
         <f t="shared" si="4"/>
-        <v>6360</v>
+        <v>8010</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B45" s="55"/>
       <c r="C45" s="2" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="F45" s="2">
         <v>2</v>
@@ -3055,110 +3067,110 @@
         <v>2</v>
       </c>
       <c r="H45" s="3">
-        <v>1480</v>
+        <v>3180</v>
       </c>
       <c r="I45" s="3">
         <f t="shared" si="4"/>
-        <v>2960</v>
+        <v>6360</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B46" s="55"/>
       <c r="C46" s="2" t="s">
-        <v>59</v>
+        <v>139</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>60</v>
+        <v>126</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H46" s="3">
-        <v>1941</v>
+        <v>1480</v>
       </c>
       <c r="I46" s="3">
         <f t="shared" si="4"/>
-        <v>5823</v>
+        <v>2960</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>61</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B47" s="55"/>
       <c r="C47" s="2" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E47" s="33" t="s">
-        <v>167</v>
+        <v>23</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="F47" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G47" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3">
-        <v>736</v>
+        <v>1941</v>
       </c>
       <c r="I47" s="3">
         <f t="shared" si="4"/>
-        <v>736</v>
+        <v>5823</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B48" s="55"/>
       <c r="C48" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>189</v>
+        <v>23</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>166</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G48" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3">
-        <v>2310</v>
+        <v>736</v>
       </c>
       <c r="I48" s="3">
         <f t="shared" si="4"/>
-        <v>4620</v>
+        <v>736</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>82</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B49" s="55"/>
       <c r="C49" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="33" t="s">
-        <v>169</v>
+        <v>23</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="F49" s="2">
         <v>2</v>
@@ -3167,26 +3179,26 @@
         <v>2</v>
       </c>
       <c r="H49" s="3">
-        <v>190</v>
+        <v>2310</v>
       </c>
       <c r="I49" s="3">
         <f t="shared" si="4"/>
-        <v>380</v>
+        <v>4620</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>170</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B50" s="55"/>
       <c r="C50" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F50" s="2">
         <v>2</v>
@@ -3195,306 +3207,306 @@
         <v>2</v>
       </c>
       <c r="H50" s="3">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="I50" s="3">
         <f t="shared" si="4"/>
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B51" s="55"/>
       <c r="C51" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>80</v>
+        <v>23</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>171</v>
       </c>
       <c r="F51" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H51" s="3">
         <v>178</v>
       </c>
       <c r="I51" s="3">
         <f t="shared" si="4"/>
-        <v>712</v>
+        <v>356</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>81</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B52" s="55"/>
       <c r="C52" s="2" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F52" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="G52" s="2">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H52" s="3">
-        <v>90</v>
+        <v>178</v>
       </c>
       <c r="I52" s="3">
         <f t="shared" si="4"/>
-        <v>1350</v>
+        <v>712</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B53" s="55"/>
       <c r="C53" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>84</v>
       </c>
       <c r="F53" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G53" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H53" s="3">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="I53" s="3">
         <f t="shared" si="4"/>
-        <v>1400</v>
+        <v>1350</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B54" s="55"/>
       <c r="C54" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D54" s="29" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" s="30" t="s">
-        <v>158</v>
+        <v>62</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G54" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H54" s="3">
-        <v>897</v>
+        <v>140</v>
       </c>
       <c r="I54" s="3">
         <f t="shared" si="4"/>
-        <v>897</v>
+        <v>1400</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>160</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B55" s="55"/>
       <c r="C55" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>77</v>
+        <v>158</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="30" t="s">
+        <v>157</v>
       </c>
       <c r="F55" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G55" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H55" s="3">
-        <v>58</v>
+        <v>897</v>
       </c>
       <c r="I55" s="3">
         <f t="shared" si="4"/>
-        <v>580</v>
+        <v>897</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B56" s="55"/>
       <c r="C56" s="2" t="s">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="F56" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G56" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H56" s="3">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="I56" s="3">
         <f t="shared" si="4"/>
-        <v>68</v>
+        <v>580</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>137</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B57" s="55"/>
       <c r="C57" s="2" t="s">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>24</v>
+        <v>135</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>73</v>
+        <v>191</v>
       </c>
       <c r="F57" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G57" s="2">
         <v>4</v>
       </c>
       <c r="H57" s="3">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="I57" s="3">
         <f t="shared" si="4"/>
-        <v>360</v>
+        <v>68</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>75</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B58" s="55"/>
       <c r="C58" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F58" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="G58" s="2">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H58" s="3">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="I58" s="3">
         <f t="shared" si="4"/>
-        <v>1652</v>
+        <v>360</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B59" s="55"/>
       <c r="C59" s="2" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>133</v>
+        <v>67</v>
       </c>
       <c r="F59" s="2">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="G59" s="2">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="H59" s="3">
         <v>59</v>
       </c>
       <c r="I59" s="3">
         <f t="shared" si="4"/>
-        <v>590</v>
+        <v>1652</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>134</v>
+        <v>69</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B60" s="55"/>
       <c r="C60" s="2" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F60" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G60" s="2">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H60" s="3">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="I60" s="3">
         <f t="shared" si="4"/>
-        <v>162</v>
+        <v>590</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B61" s="55"/>
       <c r="C61" s="2" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F61" s="2">
         <v>2</v>
@@ -3503,26 +3515,26 @@
         <v>2</v>
       </c>
       <c r="H61" s="3">
-        <v>170</v>
+        <v>81</v>
       </c>
       <c r="I61" s="3">
         <f t="shared" si="4"/>
-        <v>340</v>
+        <v>162</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B62" s="55"/>
       <c r="C62" s="2" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>146</v>
+        <v>129</v>
       </c>
       <c r="F62" s="2">
         <v>2</v>
@@ -3531,139 +3543,139 @@
         <v>2</v>
       </c>
       <c r="H62" s="3">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="I62" s="3">
         <f t="shared" si="4"/>
-        <v>204</v>
+        <v>340</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B63" s="55"/>
       <c r="C63" s="2" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="F63" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G63" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H63" s="3">
-        <v>49</v>
+        <v>102</v>
       </c>
       <c r="I63" s="3">
         <f t="shared" si="4"/>
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B64" s="55"/>
       <c r="C64" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F64" s="2">
-        <f>7+20+6</f>
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="G64" s="2">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H64" s="3">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="I64" s="3">
         <f t="shared" si="4"/>
-        <v>1320</v>
+        <v>196</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B65" s="55"/>
       <c r="C65" s="2" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>71</v>
+        <v>160</v>
       </c>
       <c r="F65" s="2">
-        <v>4</v>
+        <f>7+20+6</f>
+        <v>33</v>
       </c>
       <c r="G65" s="2">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H65" s="3">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="I65" s="3">
         <f t="shared" si="4"/>
-        <v>208</v>
+        <v>1320</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>72</v>
+        <v>162</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B66" s="55"/>
       <c r="C66" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H66" s="3">
-        <v>241</v>
+        <v>52</v>
       </c>
       <c r="I66" s="3">
         <f t="shared" si="4"/>
-        <v>482</v>
+        <v>208</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B67" s="55"/>
       <c r="C67" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F67" s="2">
         <v>2</v>
@@ -3672,125 +3684,125 @@
         <v>2</v>
       </c>
       <c r="H67" s="3">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="I67" s="3">
         <f t="shared" si="4"/>
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B68" s="56"/>
+      <c r="B68" s="55"/>
       <c r="C68" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F68" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G68" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H68" s="3">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="I68" s="3">
         <f t="shared" si="4"/>
+        <v>460</v>
+      </c>
+      <c r="J68" s="9" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B69" s="56"/>
+      <c r="C69" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F69" s="2">
+        <v>6</v>
+      </c>
+      <c r="G69" s="2">
+        <v>6</v>
+      </c>
+      <c r="H69" s="3">
+        <v>68</v>
+      </c>
+      <c r="I69" s="3">
+        <f t="shared" si="4"/>
         <v>408</v>
       </c>
-      <c r="J68" s="9" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B69" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="C69" s="22"/>
-      <c r="D69" s="22"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="22"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="24">
-        <f>SUM(I70:I75)</f>
+      <c r="J69" s="9" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B70" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C70" s="22"/>
+      <c r="D70" s="22"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="24">
+        <f>SUM(I71:I76)</f>
         <v>10509</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B70" s="47"/>
-      <c r="C70" s="5" t="s">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B71" s="47"/>
+      <c r="C71" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F70" s="5">
-        <v>1</v>
-      </c>
-      <c r="G70" s="5">
-        <v>1</v>
-      </c>
-      <c r="H70" s="6">
+      <c r="F71" s="5">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5">
+        <v>1</v>
+      </c>
+      <c r="H71" s="6">
         <v>7635</v>
-      </c>
-      <c r="I70" s="6">
-        <f>G70*H70</f>
-        <v>7635</v>
-      </c>
-      <c r="J70" s="9" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B71" s="48"/>
-      <c r="C71" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="D71" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="F71" s="5">
-        <v>3</v>
-      </c>
-      <c r="G71" s="5">
-        <v>3</v>
-      </c>
-      <c r="H71" s="6">
-        <v>500</v>
       </c>
       <c r="I71" s="6">
         <f>G71*H71</f>
-        <v>1500</v>
+        <v>7635</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B72" s="48"/>
       <c r="C72" s="5" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="F72" s="5">
         <v>3</v>
@@ -3799,54 +3811,54 @@
         <v>3</v>
       </c>
       <c r="H72" s="6">
-        <v>68</v>
+        <v>500</v>
       </c>
       <c r="I72" s="6">
-        <f t="shared" ref="I72:I74" si="5">G72*H72</f>
-        <v>204</v>
+        <f>G72*H72</f>
+        <v>1500</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>116</v>
+        <v>184</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B73" s="48"/>
       <c r="C73" s="5" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>193</v>
+        <v>92</v>
       </c>
       <c r="F73" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G73" s="5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H73" s="6">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="I73" s="6">
-        <f t="shared" si="5"/>
-        <v>240</v>
+        <f t="shared" ref="I73:I75" si="5">G73*H73</f>
+        <v>204</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B74" s="48"/>
       <c r="C74" s="5" t="s">
-        <v>69</v>
+        <v>161</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F74" s="5">
         <v>6</v>
@@ -3855,116 +3867,124 @@
         <v>6</v>
       </c>
       <c r="H74" s="6">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="I74" s="6">
         <f t="shared" si="5"/>
+        <v>240</v>
+      </c>
+      <c r="J74" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B75" s="48"/>
+      <c r="C75" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F75" s="5">
+        <v>6</v>
+      </c>
+      <c r="G75" s="5">
+        <v>6</v>
+      </c>
+      <c r="H75" s="6">
+        <v>85</v>
+      </c>
+      <c r="I75" s="6">
+        <f t="shared" si="5"/>
         <v>510</v>
       </c>
-      <c r="J74" s="9" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B75" s="49"/>
-      <c r="C75" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D75" s="5" t="s">
+      <c r="J75" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B76" s="49"/>
+      <c r="C76" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F76" s="5">
+        <v>3</v>
+      </c>
+      <c r="G76" s="5">
+        <v>3</v>
+      </c>
+      <c r="H76" s="6">
+        <v>140</v>
+      </c>
+      <c r="I76" s="6">
+        <f>G76*H76</f>
+        <v>420</v>
+      </c>
+      <c r="J76" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B77" s="13"/>
+      <c r="C77" s="10"/>
+      <c r="D77" s="10"/>
+      <c r="E77" s="10"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="B78" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="F75" s="5">
-        <v>3</v>
-      </c>
-      <c r="G75" s="5">
-        <v>3</v>
-      </c>
-      <c r="H75" s="6">
-        <v>140</v>
-      </c>
-      <c r="I75" s="6">
-        <f>G75*H75</f>
-        <v>420</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B76" s="13"/>
-      <c r="C76" s="10"/>
-      <c r="D76" s="10"/>
-      <c r="E76" s="10"/>
-      <c r="F76" s="11"/>
-      <c r="G76" s="11"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B77" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="C77" s="44"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14">
-        <f>I3+I9+I22+I28+I30+I36+I69</f>
-        <v>340588</v>
-      </c>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A79" s="34" t="s">
-        <v>207</v>
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="31"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14">
+        <f>I3+I10+I23+I29+I31+I37+I70</f>
+        <v>350348</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="B80" s="41" t="s">
+      <c r="A80" s="34" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B81" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C81" s="42"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="35"/>
+      <c r="F81" s="35"/>
+      <c r="G81" s="35"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B82" s="39"/>
+      <c r="C82" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C80" s="42"/>
-      <c r="D80" s="35"/>
-      <c r="E80" s="35"/>
-      <c r="F80" s="35"/>
-      <c r="G80" s="35"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B81" s="39"/>
-      <c r="C81" s="2" t="s">
+      <c r="D82" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E82" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F81" s="2">
-        <v>1</v>
-      </c>
-      <c r="G81" s="2">
-        <v>1</v>
-      </c>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B82" s="40"/>
-      <c r="C82" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="F82" s="2">
         <v>1</v>
@@ -3974,88 +3994,109 @@
       </c>
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
-      <c r="J82" s="9" t="s">
-        <v>206</v>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B83" s="40"/>
+      <c r="C83" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F83" s="2">
+        <v>1</v>
+      </c>
+      <c r="G83" s="2">
+        <v>1</v>
+      </c>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="9" t="s">
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B82:B83"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B10:B21"/>
-    <mergeCell ref="B31:B35"/>
-    <mergeCell ref="B23:B27"/>
-    <mergeCell ref="B37:B68"/>
-    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="B4:B9"/>
+    <mergeCell ref="B11:B22"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B38:B69"/>
+    <mergeCell ref="B71:B76"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <hyperlinks>
-    <hyperlink ref="J29" r:id="rId1" xr:uid="{16F66288-6245-48F6-9127-58AACEC69523}"/>
-    <hyperlink ref="J15" r:id="rId2" xr:uid="{63D6F597-30D0-478D-AD7F-BE9842A28425}"/>
-    <hyperlink ref="J19" r:id="rId3" xr:uid="{A288C923-0EA8-47B0-95FF-F697D2BA3F3D}"/>
-    <hyperlink ref="J17" r:id="rId4" xr:uid="{FDEE0E6F-A921-416C-95B6-8808A9B8EF28}"/>
-    <hyperlink ref="J20" r:id="rId5" xr:uid="{CC25CD88-C4A6-4402-9EAF-CF9F03244A94}"/>
-    <hyperlink ref="J16" r:id="rId6" xr:uid="{8B264363-2167-4322-AC9D-61EEEB1F631E}"/>
-    <hyperlink ref="J33" r:id="rId7" xr:uid="{A66669A8-27A1-4491-BF8D-462003BC8225}"/>
-    <hyperlink ref="J52" r:id="rId8" xr:uid="{D484C0DB-C886-4F67-B728-6E53738B4676}"/>
-    <hyperlink ref="J46" r:id="rId9" xr:uid="{D5216D90-A293-4CC2-B82E-7064EFFDA08C}"/>
-    <hyperlink ref="J47" r:id="rId10" xr:uid="{96AD8113-8FFA-46ED-9392-15D8ABA12678}"/>
-    <hyperlink ref="J48" r:id="rId11" xr:uid="{C02C3228-27CC-47C8-A83F-786A63F3C2BE}"/>
-    <hyperlink ref="J49" r:id="rId12" xr:uid="{28DA39A7-4C61-4416-A892-C421F67FB370}"/>
-    <hyperlink ref="J54" r:id="rId13" xr:uid="{17AE1DE1-C7FE-4821-8E54-733DA2DEEFAE}"/>
-    <hyperlink ref="J64" r:id="rId14" xr:uid="{DC184D76-5B0F-48B1-B9DA-1D3075C61C4A}"/>
-    <hyperlink ref="J63" r:id="rId15" xr:uid="{5787A380-0DF6-43B5-996A-DF9BFE7D219C}"/>
-    <hyperlink ref="J58" r:id="rId16" xr:uid="{DF5E9123-54AB-42AB-82D2-D37699101243}"/>
-    <hyperlink ref="J65" r:id="rId17" xr:uid="{4E13B782-BC36-409D-8B4F-5BC97EAAA87D}"/>
-    <hyperlink ref="J57" r:id="rId18" xr:uid="{F9B86FEA-78B3-468C-B03B-0D93439F7ABD}"/>
-    <hyperlink ref="J55" r:id="rId19" xr:uid="{D197653E-A28E-4309-8A92-274076756833}"/>
-    <hyperlink ref="J51" r:id="rId20" xr:uid="{4A67E8D4-9CDB-42BA-BC51-D3ED5858EB3C}"/>
-    <hyperlink ref="J53" r:id="rId21" xr:uid="{24D0308A-22D0-4EA8-BF18-CB74A877A9ED}"/>
-    <hyperlink ref="J14" r:id="rId22" xr:uid="{07798078-5EF2-418B-926B-32B085A8EAB3}"/>
-    <hyperlink ref="J26" r:id="rId23" xr:uid="{6AD5C335-A479-4D1D-BE86-7C59DF0CAF54}"/>
-    <hyperlink ref="J24" r:id="rId24" xr:uid="{05668A5F-8025-48FA-BEE6-2CDC77003EDF}"/>
-    <hyperlink ref="J25" r:id="rId25" xr:uid="{5DE36C82-2916-4073-8BCB-B11CA92B4A85}"/>
-    <hyperlink ref="J21" r:id="rId26" xr:uid="{621916B0-703A-4ABD-836A-01E69D9F433B}"/>
-    <hyperlink ref="J27" r:id="rId27" xr:uid="{114EE048-6FD6-4606-B599-172DD13FA3F8}"/>
-    <hyperlink ref="J66" r:id="rId28" xr:uid="{A4D718D4-6198-4FE8-B15E-10173BA491E8}"/>
-    <hyperlink ref="J67" r:id="rId29" xr:uid="{F8B4AA82-7C18-466B-9A3F-52CC4EC9FEEF}"/>
-    <hyperlink ref="J68" r:id="rId30" xr:uid="{903E7A31-2228-48A6-B9CE-D779283321E0}"/>
-    <hyperlink ref="J32" r:id="rId31" xr:uid="{11E06CED-B5BE-4EE5-AD4E-A7DE1E24CB6F}"/>
-    <hyperlink ref="J34" r:id="rId32" xr:uid="{950DA2AB-4F1A-4AF5-97E8-BE09B2A4CF7F}"/>
-    <hyperlink ref="J35" r:id="rId33" xr:uid="{B1851711-0DAB-41CB-A077-003B128D248E}"/>
-    <hyperlink ref="J11" r:id="rId34" xr:uid="{68F08CBF-43FA-4141-9AD8-5D89AC72B358}"/>
-    <hyperlink ref="K13" r:id="rId35" xr:uid="{C2EEEAAD-E501-48FA-AA64-1A5F3B193710}"/>
-    <hyperlink ref="J45" r:id="rId36" xr:uid="{B1F324AE-5327-46E7-8281-E258EEC5109F}"/>
-    <hyperlink ref="J61" r:id="rId37" xr:uid="{C5C341A3-7D12-45AC-9068-1F42F628D595}"/>
-    <hyperlink ref="J59" r:id="rId38" xr:uid="{59B3973E-3E99-4A02-BA55-12D93D0FFCAF}"/>
-    <hyperlink ref="J56" r:id="rId39" xr:uid="{F73B4C48-F126-4ABB-A25B-44CAB6EBCE08}"/>
-    <hyperlink ref="J23" r:id="rId40" xr:uid="{1ACD4BA2-51F9-4DBA-9CBC-10CB869FB5CF}"/>
-    <hyperlink ref="J60" r:id="rId41" xr:uid="{F5F44425-0FC4-4561-9DB0-5367C1F085DC}"/>
-    <hyperlink ref="J62" r:id="rId42" xr:uid="{6A6035A7-2DA9-400C-9CAC-A25336AAA7DA}"/>
-    <hyperlink ref="J13" r:id="rId43" xr:uid="{464DBC11-F2E4-4FF7-AFD0-D95603482D38}"/>
-    <hyperlink ref="J12" r:id="rId44" xr:uid="{4EE6AE69-2A48-468E-AA96-8013A302C145}"/>
-    <hyperlink ref="J10" r:id="rId45" xr:uid="{1B99D7DE-E976-4C33-9E1D-B70C9D1D8356}"/>
-    <hyperlink ref="J50" r:id="rId46" xr:uid="{AE9D1FE1-BE58-4174-8C84-96F3EEEB9F29}"/>
-    <hyperlink ref="J71" r:id="rId47" xr:uid="{90DDBC3E-ABF8-4863-B731-02D735ED60A1}"/>
-    <hyperlink ref="J72" r:id="rId48" xr:uid="{BBD202E7-6C40-4C9A-BC68-6C629F5863A5}"/>
-    <hyperlink ref="J73" r:id="rId49" xr:uid="{DC4DA8CC-ECF9-4A4B-BC07-92BF171CDB99}"/>
-    <hyperlink ref="J74" r:id="rId50" xr:uid="{05A0F23A-15E0-4E82-83B8-B0EAF8BEF4ED}"/>
-    <hyperlink ref="J75" r:id="rId51" xr:uid="{56483B67-33AC-4EE2-AE3A-287085827DBF}"/>
-    <hyperlink ref="J18" r:id="rId52" xr:uid="{87309477-8CF1-4FC2-B823-390F8D78DF65}"/>
-    <hyperlink ref="J82" r:id="rId53" xr:uid="{D4C388B4-8E78-4F09-BBEE-DF7C93641240}"/>
-    <hyperlink ref="J31" r:id="rId54" xr:uid="{5B24EF0F-C6A4-47E1-8CC7-ED00C25C7AC3}"/>
-    <hyperlink ref="J37:J44" r:id="rId55" display="https://meviy.misumi-ec.com/ja-jp/" xr:uid="{FDBD395D-3BD0-48FC-B50D-2052192C0F1C}"/>
-    <hyperlink ref="J70" r:id="rId56" xr:uid="{4E136A16-60EE-456F-85D3-252B93C80D51}"/>
+    <hyperlink ref="J30" r:id="rId1" xr:uid="{16F66288-6245-48F6-9127-58AACEC69523}"/>
+    <hyperlink ref="J16" r:id="rId2" xr:uid="{63D6F597-30D0-478D-AD7F-BE9842A28425}"/>
+    <hyperlink ref="J20" r:id="rId3" xr:uid="{A288C923-0EA8-47B0-95FF-F697D2BA3F3D}"/>
+    <hyperlink ref="J18" r:id="rId4" xr:uid="{FDEE0E6F-A921-416C-95B6-8808A9B8EF28}"/>
+    <hyperlink ref="J21" r:id="rId5" xr:uid="{CC25CD88-C4A6-4402-9EAF-CF9F03244A94}"/>
+    <hyperlink ref="J17" r:id="rId6" xr:uid="{8B264363-2167-4322-AC9D-61EEEB1F631E}"/>
+    <hyperlink ref="J34" r:id="rId7" xr:uid="{A66669A8-27A1-4491-BF8D-462003BC8225}"/>
+    <hyperlink ref="J53" r:id="rId8" xr:uid="{D484C0DB-C886-4F67-B728-6E53738B4676}"/>
+    <hyperlink ref="J47" r:id="rId9" xr:uid="{D5216D90-A293-4CC2-B82E-7064EFFDA08C}"/>
+    <hyperlink ref="J48" r:id="rId10" xr:uid="{96AD8113-8FFA-46ED-9392-15D8ABA12678}"/>
+    <hyperlink ref="J49" r:id="rId11" xr:uid="{C02C3228-27CC-47C8-A83F-786A63F3C2BE}"/>
+    <hyperlink ref="J50" r:id="rId12" xr:uid="{28DA39A7-4C61-4416-A892-C421F67FB370}"/>
+    <hyperlink ref="J55" r:id="rId13" xr:uid="{17AE1DE1-C7FE-4821-8E54-733DA2DEEFAE}"/>
+    <hyperlink ref="J65" r:id="rId14" xr:uid="{DC184D76-5B0F-48B1-B9DA-1D3075C61C4A}"/>
+    <hyperlink ref="J64" r:id="rId15" xr:uid="{5787A380-0DF6-43B5-996A-DF9BFE7D219C}"/>
+    <hyperlink ref="J59" r:id="rId16" xr:uid="{DF5E9123-54AB-42AB-82D2-D37699101243}"/>
+    <hyperlink ref="J66" r:id="rId17" xr:uid="{4E13B782-BC36-409D-8B4F-5BC97EAAA87D}"/>
+    <hyperlink ref="J58" r:id="rId18" xr:uid="{F9B86FEA-78B3-468C-B03B-0D93439F7ABD}"/>
+    <hyperlink ref="J56" r:id="rId19" xr:uid="{D197653E-A28E-4309-8A92-274076756833}"/>
+    <hyperlink ref="J52" r:id="rId20" xr:uid="{4A67E8D4-9CDB-42BA-BC51-D3ED5858EB3C}"/>
+    <hyperlink ref="J54" r:id="rId21" xr:uid="{24D0308A-22D0-4EA8-BF18-CB74A877A9ED}"/>
+    <hyperlink ref="J15" r:id="rId22" xr:uid="{07798078-5EF2-418B-926B-32B085A8EAB3}"/>
+    <hyperlink ref="J27" r:id="rId23" xr:uid="{6AD5C335-A479-4D1D-BE86-7C59DF0CAF54}"/>
+    <hyperlink ref="J25" r:id="rId24" xr:uid="{05668A5F-8025-48FA-BEE6-2CDC77003EDF}"/>
+    <hyperlink ref="J26" r:id="rId25" xr:uid="{5DE36C82-2916-4073-8BCB-B11CA92B4A85}"/>
+    <hyperlink ref="J22" r:id="rId26" xr:uid="{621916B0-703A-4ABD-836A-01E69D9F433B}"/>
+    <hyperlink ref="J28" r:id="rId27" xr:uid="{114EE048-6FD6-4606-B599-172DD13FA3F8}"/>
+    <hyperlink ref="J67" r:id="rId28" xr:uid="{A4D718D4-6198-4FE8-B15E-10173BA491E8}"/>
+    <hyperlink ref="J68" r:id="rId29" xr:uid="{F8B4AA82-7C18-466B-9A3F-52CC4EC9FEEF}"/>
+    <hyperlink ref="J69" r:id="rId30" xr:uid="{903E7A31-2228-48A6-B9CE-D779283321E0}"/>
+    <hyperlink ref="J33" r:id="rId31" xr:uid="{11E06CED-B5BE-4EE5-AD4E-A7DE1E24CB6F}"/>
+    <hyperlink ref="J35" r:id="rId32" xr:uid="{950DA2AB-4F1A-4AF5-97E8-BE09B2A4CF7F}"/>
+    <hyperlink ref="J36" r:id="rId33" xr:uid="{B1851711-0DAB-41CB-A077-003B128D248E}"/>
+    <hyperlink ref="J12" r:id="rId34" xr:uid="{68F08CBF-43FA-4141-9AD8-5D89AC72B358}"/>
+    <hyperlink ref="K14" r:id="rId35" xr:uid="{C2EEEAAD-E501-48FA-AA64-1A5F3B193710}"/>
+    <hyperlink ref="J46" r:id="rId36" xr:uid="{B1F324AE-5327-46E7-8281-E258EEC5109F}"/>
+    <hyperlink ref="J62" r:id="rId37" xr:uid="{C5C341A3-7D12-45AC-9068-1F42F628D595}"/>
+    <hyperlink ref="J60" r:id="rId38" xr:uid="{59B3973E-3E99-4A02-BA55-12D93D0FFCAF}"/>
+    <hyperlink ref="J57" r:id="rId39" xr:uid="{F73B4C48-F126-4ABB-A25B-44CAB6EBCE08}"/>
+    <hyperlink ref="J24" r:id="rId40" xr:uid="{1ACD4BA2-51F9-4DBA-9CBC-10CB869FB5CF}"/>
+    <hyperlink ref="J61" r:id="rId41" xr:uid="{F5F44425-0FC4-4561-9DB0-5367C1F085DC}"/>
+    <hyperlink ref="J63" r:id="rId42" xr:uid="{6A6035A7-2DA9-400C-9CAC-A25336AAA7DA}"/>
+    <hyperlink ref="J14" r:id="rId43" xr:uid="{464DBC11-F2E4-4FF7-AFD0-D95603482D38}"/>
+    <hyperlink ref="J13" r:id="rId44" xr:uid="{4EE6AE69-2A48-468E-AA96-8013A302C145}"/>
+    <hyperlink ref="J11" r:id="rId45" xr:uid="{1B99D7DE-E976-4C33-9E1D-B70C9D1D8356}"/>
+    <hyperlink ref="J51" r:id="rId46" xr:uid="{AE9D1FE1-BE58-4174-8C84-96F3EEEB9F29}"/>
+    <hyperlink ref="J72" r:id="rId47" xr:uid="{90DDBC3E-ABF8-4863-B731-02D735ED60A1}"/>
+    <hyperlink ref="J73" r:id="rId48" xr:uid="{BBD202E7-6C40-4C9A-BC68-6C629F5863A5}"/>
+    <hyperlink ref="J74" r:id="rId49" xr:uid="{DC4DA8CC-ECF9-4A4B-BC07-92BF171CDB99}"/>
+    <hyperlink ref="J75" r:id="rId50" xr:uid="{05A0F23A-15E0-4E82-83B8-B0EAF8BEF4ED}"/>
+    <hyperlink ref="J76" r:id="rId51" xr:uid="{56483B67-33AC-4EE2-AE3A-287085827DBF}"/>
+    <hyperlink ref="J19" r:id="rId52" xr:uid="{87309477-8CF1-4FC2-B823-390F8D78DF65}"/>
+    <hyperlink ref="J83" r:id="rId53" xr:uid="{D4C388B4-8E78-4F09-BBEE-DF7C93641240}"/>
+    <hyperlink ref="J32" r:id="rId54" xr:uid="{5B24EF0F-C6A4-47E1-8CC7-ED00C25C7AC3}"/>
+    <hyperlink ref="J38:J45" r:id="rId55" display="https://meviy.misumi-ec.com/ja-jp/" xr:uid="{FDBD395D-3BD0-48FC-B50D-2052192C0F1C}"/>
+    <hyperlink ref="J71" r:id="rId56" xr:uid="{4E136A16-60EE-456F-85D3-252B93C80D51}"/>
     <hyperlink ref="J4" r:id="rId57" xr:uid="{272C059B-1D1E-4FA7-9A73-EBA0704A055E}"/>
-    <hyperlink ref="J5" r:id="rId58" xr:uid="{0DCA6E50-1A77-4787-BDAF-E2F530E5F5A5}"/>
-    <hyperlink ref="J6" r:id="rId59" xr:uid="{CBAC2EE7-F2BC-4255-BA66-1B704B3DA056}"/>
-    <hyperlink ref="J7" r:id="rId60" xr:uid="{28FFAE5B-B7BE-42FD-BCA4-4EE6B32AA1E9}"/>
-    <hyperlink ref="J8" r:id="rId61" xr:uid="{99EA8925-0994-41B9-BC80-375EA21AA671}"/>
+    <hyperlink ref="J6" r:id="rId58" xr:uid="{0DCA6E50-1A77-4787-BDAF-E2F530E5F5A5}"/>
+    <hyperlink ref="J7" r:id="rId59" xr:uid="{CBAC2EE7-F2BC-4255-BA66-1B704B3DA056}"/>
+    <hyperlink ref="J8" r:id="rId60" xr:uid="{28FFAE5B-B7BE-42FD-BCA4-4EE6B32AA1E9}"/>
+    <hyperlink ref="J9" r:id="rId61" xr:uid="{99EA8925-0994-41B9-BC80-375EA21AA671}"/>
+    <hyperlink ref="J5" r:id="rId62" xr:uid="{FCD34A8B-ED9C-464A-9233-8CD17D38E6D4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId62"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId63"/>
 </worksheet>
 </file>